--- a/data/outputs/concept_frequency_consensus.xlsx
+++ b/data/outputs/concept_frequency_consensus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Concept Frequencies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Consensus Labels" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concept Frequencies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consensus Labels" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>community impact</t>
+          <t>CHW Empowerment Through Training</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -463,106 +463,106 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>community impact</t>
+          <t>CHW Empowerment Through Training</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>community impact</t>
+          <t>CHW-Led Infectious Disease Management</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5660000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>CHW-Led Infectious Disease Management</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>0.6344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Children Served</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Children Served</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>knowledge sharing</t>
+          <t>Clinical Interventions by CHWs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -571,106 +571,106 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>knowledge sharing</t>
+          <t>Clinical Interventions by CHWs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>knowledge sharing</t>
+          <t>Community Empowerment Through Education</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Community Empowerment Through Education</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Disease Burden</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Disease Burden</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>Drug Abuse: Environment and Awareness</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -679,46 +679,1072 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6333333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>Drug Abuse: Environment and Awareness</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>Elderly Served</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5333333333333333</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Elderly Served</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Financial Hardship</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Financial Hardship</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence (GBV) and Child Protection</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence (GBV) and Child Protection</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.04600000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.424</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.496</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Lack of Follow-Through</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lack of Follow-Through</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.03800000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.134</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>25</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.308</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Material or Training Requests</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Material or Training Requests</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>25</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>25</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.07600000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>25</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Education and Challenges</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>25</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Education and Challenges</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>25</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mental Health Awareness and Support</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>25</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.064</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Mental Health Awareness and Support</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>25</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Mental or Emotional Distress</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Mental or Emotional Distress</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>25</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>25</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>25</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>25</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Nutrition Education and Food Access</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>25</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Nutrition Education and Food Access</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>25</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.08800000000000001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Overburdened CHWs</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>25</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Overburdened CHWs</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>25</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>25</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.6080000000000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>25</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>25</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.504</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>25</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.594</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Resource and Material Distribution</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>25</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.07600000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Resource and Material Distribution</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>25</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sexual and Reproductive Health Education</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.148</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sexual and Reproductive Health Education</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>25</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.1488</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Social Isolation</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>25</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Social Isolation</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>25</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Stigma or Discrimination</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>25</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.068</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Stigma or Discrimination</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>25</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>25</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.588</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>25</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>25</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>25</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.198</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>25</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.412</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>25</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.318</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>25</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>25</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>25</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.428</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>25</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.4379999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -732,7 +1758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,36 +1776,300 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>After receiving training from WiRED, I was able to teach others in my village about malaria prevention. The community now trusts me and people ask me for advice all the time.</t>
+          <t>Abortion Abortion is very deadly because one can bleed to death. Some have been able to heal from post abortion hemorrhage, but some end up having anemia. This topic has been left out, yet it is very important because we have many of our young girls are dying from excess bleeding from abortion. I talked to a group of young girls who agreed to open up about their abortion experience and none of them enjoyed even a bit of it. I agreed with them that there would be no more abortion. Those above 20, they should go for family planning and the rest to practice ---</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'training': 1, 'trust': 1, 'community impact': 1, 'confidence': 1, 'knowledge sharing': 1}</t>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I visit homes and share information about clean water. People now recognize me as a health worker.</t>
+          <t>Asthma Asthma is a chronic disease which can affect everyone. I spotted a young child wheezing and as I inquired from the mother, she told me that she was suspecting that the child might be having common cold as the child was coughing due to change of weather. But to me as a CHW I thought that it would be best if the child was to be taken to the hospital for medical examination so that the mother could know what was wrong with the child. With my help, I referred the ??? to take the child to the hospital. The child was tested and was found to be ailing from asthma. The child was put onto medication and as now the child showing some improvements. Though asthma is a chronic disease, if proper medication and continuous taking of the drugs is well conducted, it can help in reducing chances of child fatality. ---</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'training': 0, 'trust': 1, 'community impact': 1, 'confidence': 1, 'knowledge sharing': 1}</t>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I had no previous experience, but after training I felt confident talking to people about disease prevention.</t>
+          <t>Tuberculosis People living in ????? settlements tend to not be concerned about their health. Many are first concerned with how they can attend to their daily labor to make some money which can help them put some food on the table. People are coughing and just take it as a normal cough. During my field work, I came across two people who were coughing as I was training them. I asked them when they started coughing and advised them to see the doctor for a tuberculosis test. They went for the test and one of them was found positive for tuberculosis. She has begun treatment and hopefully she will be okay. As CHW, I am now talking to many and also refer them for tuberculosis test at ???? ---</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'training': 1, 'trust': 0, 'community impact': 0, 'confidence': 1, 'knowledge sharing': 1}</t>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 1, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Financial Hardship': 1, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tuberculosis During my fieldwork engagement with my participants in a training, one of my participants approached me after I had completed my training—and asked me if I could be able to allow him share with me something. I first thought what could he wanted to tell me, yet I gave time for questions during the sessions. And he could not ask anything. Bravely enough, I heeded to his request and he shared with me that he was diagnosed with tuberculosis and he was put into medication but unfortunately, he defaulted. He wanted to know if I could help him get back to medication but was not happy to go back to Thramogi Agmga Teaching and Referral Hospital since they could not help him. I managed to refer him to KNAP and he got helped and now his life is improving day by day. I am doing close follow-up on him to make sure he has taken his drugs. ---</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 1, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>COVID-19 Coronavirus continues to be a menace not only to the country but also to our work, as it restricts large gatherings and restricts people to minimal contact with each other to avoid the spread of the virus. The country is currently battling the third Indian wave which has shown more devastating effects of the new strain of the virus. This has led to more restrictions and also has led to the imposed curfews within Kisumu County and the environs. There is a possibility of even more stringent measures to curb the third wave. Having trained as a Community Health Worker, I have been actively sensitizing and creating awareness to my community members on the preventive measures against the COVID-19 pandemic. I have been emphasizing a lot on the benefits of putting on masks, washing hands with clean running water and soap, sanitizing and also keeping social distance. Through this, the members of the community have embraced and also adopted the teachings and are always doing what I have trained them to do. This has made me very happy because there is no single case that has been reported from this community I live and work in. Were it by any chance that the people were not sensitized, then this community could be a COVID-19 hotspot and many people could have died. There’s a big change on how people wash their hands and also put on masks compared to other previous years where people did not take washing hands with soap and running water very important. Initially, many people could even take or rather eat fruits or any other food stuffs without washing their hands but since COVID-19 hit us, many people have adopted the trend of washing hands regularly. This is a great change that has manifested in my community. ---</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>COVID-19 Regarding the COVID-19 new variant, since most of the community members took vaccines, many people have left the common practices which were given by the Ministry of Health such as washing hands, putting on masks, avoiding crowded places, and keeping social distance. Political rallies in Kenya have attracted so many crowds that has contributed to many people contracting the disease. Omicron wave was reported in Kenya some few weeks back and we have seen cases of the Omicron is rising day by day. As a CHW, I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures and about mobilizing these who have not been vaccinated to go for vaccinations. ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 0, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Malaria Having malaria is a very bad experience that personally I would not like to get sick again. Physical symptoms that I had was fatigue, vomiting, fever, and sometimes diarrhea. In the evening a strong headache and chills appeared as if it had been stirred up or triggered by something. Sincerely speaking, when I felt symptoms coming on, I used to go over the counter and buy malaria drugs—e.g., ACTM—because I thought that every symptom as such could be malaria which I realized after becoming a CHW that it was not a good idea. Malaria could return again and again because I was not adhering to the instructions of completing doses, I was not treating malaria well, not sleeping under mosquito treated net. As a CHW, what I can do to help people with malaria is to advise them to go to the hospital and get tested and also to be treated well whenever the symptoms occur. ---</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 0, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a bacterial infection caused by plasmodium vale that affects the blood stream of human body. It is spread through anopheles mosquito bite from one person to another. People who have malaria usually feel sick with high fever and shaking chills. Some people may experience signs in the abdomen or muscles, fatigue, fever, night sweats, shivering, nausea, diarrhea, vomiting, headache, and coldness. The physical symptoms of malaria may include vomiting, tiredness, shivering, body weakness, sweating, children might be restless. The immediate action I take as a Community Health Worker when I see the symptoms coming is to do the sponging to reduce temperature, drink a lot of water due to vomiting and diarrhea. This are the first aid you do before going to the hospital. The malaria infection may return time and again if the patient does not follow the preventive measures like sleeping under the treated mosquito nets and vector control. As a Community Health Worker, if you once identify someone suffering from malaria, I immediately refer to the nearest health center. Many people have died from malaria due to late diagnosis that might lead to anemia, enlarged spleen that leads to ????????? that have similar symptoms as malaria. Disease like typhoid, dysentery. So, if not careful, you might miss the diagnosis, so you must thoroughly and probe the client. You should be well conversant with the signs and symptoms of malaria. And thus, the slogan “ZERO MALARIA STARTS WITH ME.” ---</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Successful Outcomes': 0, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Malaria The weather in Kisumu has totally changed, there is a lot of rains and floodings experienced everywhere. This rain has also brought a lot of stagnant water which helps mosquitoes breed. During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria. I also came across one of my participants who was having malaria but was just using over-the-counter drugs. I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test which later turned positive and he was treated and given prescriptions of the medicines. As a CHW, I am very happy that the person is responding well to medications. ---</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 1, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Malaria This story is all about my personal experience with malaria in the past and also sharing on what I have been doing to help people to not get malaria. My first diagnosis on malaria was in four years back. I fell sick and could not know what I was suffering from. My body was very weak, mostly my body joints. My heart was almost bursting. My body temperature was very high. I was sweating a lot and during morning hours I was feeling a lot of cold which made me to sit outside my room to find heat from the sun. It was unbearable. This time I was not a trained Community Health Worker, so I had no information about malaria. The only treatment I was able to go for was only pain killers which I was buying through over-the-counter. And this was ?????? blood sample was taken to the lab, here is where I got myself diagnosed the malaria. I was treated and got better within two weeks and a half. By all this time, I was not sleeping under the net so the mosquitos were enjoying sucking my blood. Now that I am a trained Community Health Worker, I have been training my community members on how they can prevent contacting malaria. In my training, I share with them on the importance of sleeping under treated mosquito nets, clearing of bushy surroundings, draining stagnant waters, and also keeping the surroundings clean so as keep away mosquitoes from breeding. ---</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Malaria During my health education at Bandani Slums-Kisumu County, giving malaria talk to the residents, I narrowed down on the signs and symptoms of malaria, the treatment and causes. Some of the causes like not sleeping under the treated mosquito nets, vector control. The signs and symptoms like high ever, shaking, chills, pain in the muscles and abdomen. Some people feel very sick, fatigue, fever, night sweats, nausea, shivering diarrhea, vomiting, headache and coldness. Upon completion, one Mrs. Mary Onyango approached me and requested that I visit her home. On our way to her homestead, she narrated to me some of the signs we talked about earlier that she has been seeing little girl experiencing. On reaching her homestead a few kilometers from where we were, I met the little girl. She was sweating all over her body. She told me she had headache; I saw her shivering and was vomiting. Based on what I saw, I concluded the child might have been suffering from malaria. I told the mother to do the sponging to reduce the temperature due to the high fever. I advised the mother to take her to the nearest health facility for further management. After two days, I did a follow-up home visit to see how the little girl was. She was given anti-malaria tablets and was responding well to the treatment. ---</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 1, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene/Teenage Pregnancy Many teenage adolescent girls and young women suffer from what we call menstrual poverty. Menstrual poverty is an incidence whereby a girl is not able to get access to menstrual aids such as sanitary towels and menstrual cups. At the beginning of December, teenage pregnancy rapid growth raised an alarm whereby many individuals and like-minded individuals came together to find out why most of our teenage girls are getting pregnant. The 16-day activism and activism that brought about ??????? for Google meets and physical meetings helped me reach out to more than 50 girls and had some chit chats. From the interactions, I found out that menstrual poverty is a major leading factor in this lack of sanitary towels during this time of the month forcing some girls to engage in transactional sex which back to these unwanted teenage pregnancies. From this I, as a CHW, decided to partner with other ??? and individuals to fundraise for pads to give these girls. This has helped reduce and prevent some if not all. Most men and adults too have been sensitized by me that menstruation is not a woman issue but a human issue and we should all support our girls during this time of the month. ---</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 1, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Financial Hardship': 1, 'Social Isolation': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease caused by a parasite called plasmodium parasite, transmitted by the bite of infected Anopheles mosquitos. Malaria spreads by animal or insect bites or stings and by blood products (unclean needles or unscreened blood). The physical symptoms are like fever, vomiting, headache, yellow skin, diarrhea, fatigue, kidney failure, seizure/confusion, sweating, muscle aches, chest pain, chills that shake the whole body, dizziness and severe symptoms such as paralysis. Therefore, in any case I feel these symptoms, some of them, not all because I may not go through all of the symptoms. Why? It may happen from time to time. It is advisable that the moment it starts, I will force myself to go to the hospital for a check-up because that is the right place for me to get treatment. Hence, it will also help me to avoid it to become severe. Malaria even treated can re-occur again and again, so it is good to take action immediately before danger. I do advise people with malaria symptoms to go for a test before taking any painkiller, because this can cause danger. I also take an action by taking some of them in hospitals so that they can get treatment. I assure them to finish the malaria dose and treatment to avoid it from reoccurring again after a short time. On the prevention side part of it, I avoid mosquito bites by using insect repellent, hence tell the community to do net. You also have to wear long-sleeved clothing and long pants if you are outdoors at night. For pregnant mothers, I tell them to go for check-up whenever they feel the symptoms because malaria affects her and the fetus. It can lead to maternal anemia, fetal loss, premature delivery, and delivery of low-birth-weight infants. So many people have died because of malaria and what causes this is ignorance. Some of the patients ignore the symptoms and also take wrong medication before tests, leading to severe infections hence death. It is good to love yourself, love and protect your life because it is given once by our creator who is God. Observe cleanliness at all cost to prevent more infections from occurring. ---</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Malaria My personal experience about malaria has been very challenging as it affects me periodically and comes unexpectedly. There is a day I fell ill at night while asleep and my symptoms were for malaria because I felt cold with shivering, then developed a high temperature accompanied by severe sweating and headache. In my case, I normally use thermometer to know if am having malaria by checking on my temperature level. If my temperature exceeds 38C or above, then I take painkillers to relief pain, only at night but if I have malaria during the day I go to the hospital. There was a time I had malaria and took Coartem as it is known to reduce malaria faster, then again visited the hospital and it did not reflect that I have malaria as compared to the time when I take painkillers. My advice to people is always to avoid using Coartem without visiting the hospital at first and rather use painkillers to relief pain. After visiting the hospital my eating a bit usually changes, I eat a lot so as to heal faster. In most cases, when I have malaria, it usually comes with migraine, so when I experience such, I take hot strong tea with a lot of sugar, then relax my mind and sleep. When I wake up, I am always free from migraine because I believe my malaria comes with headache followed by migraine. ---</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 0, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Malaria People who have malaria usually feel very sick with high fever and shaking chills. However, the introduction malaria vaccine as a preventive measure for the disease has been seen as a huge step in the fight against the disease. Although WHO has approved the vaccine to be used in children in countries with high number of cases, the disease still remains the number one killer of children. According to a client whom I met during our health education session, her experience with malaria was that she lost her appetite after the attack. She further stated that she had alternating body temperature which was at times cold and at times very hot. She noted that the alternating body temperatures were accompanied by high fever, vomiting of yellowish substance, body aches and fatigue. The client observed that she also lost a significant body weight due to her missing meals because of lost appetite. She later went to seek medical attention a few days when the symptoms persisted. Her experience with malaria is not different from mine. I had encounter with malaria a year ago where the symptoms included high body temperature, fatigue, body ache and high fever. As CHWs, we urge people to prevent themselves from malaria by visiting health centers whenever they experience such symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fibroids In the field I came across this woman who was suffering from fibroids, and she had very low self-esteem because she believed she had cancer and cancers are untreatable. I was touched when she told me she was only awaiting her death. I don’t know much about fibroids, but the little I know about it managed to cheer her up and build up her self-esteem once again. When I assured her that fibroids are non-cancerous growths, she said that the doctor also told her the same, but she could not believe it because doctors love telling people good lies so that they don’t give up in life. But since I also said the same, she promised to start going to treatment and also work on her self-esteem. I will be checking up on her just to lift up her spirits. ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 1, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>First Aid for Nose Bleed During nose bleed, blood flows from one or both nostrils. It can be heavy or light and last from a few seconds to 15 minutes or more. I came across a patient who had nose bleeding each time and she did not know what to do. I told her how to stop it by: sitting down and firmly pinch the soft part of your nose, just above your nostrils, for at least 10-15 minutes. Lean forward and breathe through your mouth. This will drain blood into your nose instead of down the back of your throat. Place an ice pack/bag or frozen vegetables covered by a towel on the bridge of your nose. Stay upright rather than lying down, as this reduces blood pressure in the blood vessels of your nose and will discourage further bleeding. At least she got relieved after doing all these leading to nose bleed occurring rarely. ---</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Obesity I am surprised even with this high cost of living and high oil prices in Kenya some of us still suffer from obesity. Nowadays this is a very rampant disease amongst the community members. I met this woman who cried to me asking me what she can do to cure her obesity. Ever since she realized she is obese, she has been trying every means to kill the fat, but to no avail. Everything, meaning she drank vinegar, traditional medicines, and all other things, but nothing seems to work. I told her the only thing she needed was exercise and a change of diet and she would be okay. She agreed to that and now we are yet to see some changes. And never forget to also have faith in that which she is doing. ---</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 0, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Malaria Malaria has been very challenging in our community there was active I was called at night that one of my clients was sick upon getting her place I noticed that she had the symptoms like that of malaria as she was shivering and had cold, and the body temperature was high too and she was also complaining of headache. And she sweating too. I took her to the nearest hospital for medication where malaria test was done and the results were positive. She was given antimalarial drugs to reduce the pain and I made sure she completed her dose as was instructed by the doctor. ---</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 1, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 0, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a serious disease caused by a parasite. When one contracts malaria, he or she feels that the body functions change gradually from being active to being tired or inactive. Malaria has physical symptoms which are fever and chills which are associated with the rupture of erythrocytic-stage schizonts. Malaria also has signs which one can feel, for example headache, muscle or joint pain, general feeling of discomfort and many others. When one feels that he or she has these signs and symptoms, they should seek medical advice immediately. Self-treatment (over-the-counter drug) is only a temporary measure and immediate medical advice or care is important. Yes, malaria can return. You can get malaria more than once even after taking the precautions that were prescribed to a patient. So one still needs to take precautions regularly to try not to get the disease. As a Community Health Worker, I would first create awareness of the disease to the community. In order the members to be aware of the disease, how it affects people, what are the precautions one needs in order not to get the disease, how one can tackle the disease when he or she has it, and many more unanswered questions. As a victim of contracting the disease more than once, the disease can interfere with your body function totally. One can feel weak and constantly vomiting and also having high fevers and many more symptoms I have not mentioned. One can seek medical care at the medical centers when he or she has these signs and symptoms. I mostly use self-treatment (over-the-counter drug) for temporary measure, but in case it is serious and cannot be contained with the over-the-counter drugs, I seek medical attention. Due to the invention of the malaria vaccines which has been approved by the World Health Organization, I know we will have positive impacts toward malaria. ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 0, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 0, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Child Nutrition Access to adequate and nutritious food is important for good health. The convention provides for the application of readily available technology for the provision of adequate nutritious food and clear drinking water. Both the state and the parent of the child have to participate in ensuring that children are now nourished nutrition support programs by the government and non-governmental organizations such as the school feeding programs in arid and semi-arid areas plays on essential role nutrition awareness programs that educate parents on how to supplement the staple food with easily available nutrients are also important. As CHW, I am thankful to KUAP, as they offer nutrition programs and teaching to young mothers on how they can handle their little ones. ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CHW Training Having been in Nyalenda for the last five years, health information in the community was not taken seriously. But after the training and we started working in the community giving health information, now they can go to the nearest facility and at the same time we do referrals. In the training, I got more information about COVID-19 even before the government COVID lockdown and how to manage COVID-19. Before training, I could not do first aid. But after the training, I have some skills and now am in a position to perform first aid before I do referrals to the facility. Patient assessment was quite challenging to me. But after being trained by Madam Winnie and Mr. Kituli, I can now do it on my own and know how to handle some of the problems and refer. With the information I have from the training and my knowledge, the community I am in today is changing gradually. They are very eager to be taught more and more about the health issues, because they have been lacking information for so long. But thanks to WiRED International for the training they gave us, because now we are able to give back to the community the information we get, and the community is impressed so much, and they are requesting that we keep on giving them the information that they had lacked for some time. I would like to thank Madam Winnie and Mr. Kituli so much for the training they gave us. It is just on another level. Thanks to Lilian for believing in us and giving us a chance to be trained. Thanks to Mr. Gary for the support you gave us during the training up to now. May God bless you. ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{'CHW Empowerment Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Resource and Material Distribution': 0, 'Monitoring and Follow-Up': 0, 'Trust and Cultural Mediation': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Successful Outcomes': 1, 'Material or Training Requests': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Financial Hardship': 0, 'Social Isolation': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Mental or Emotional Distress': 0, 'Lack of Resources': 1, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Follow-Through': 0, 'Lack of Knowledge': 1}</t>
         </is>
       </c>
     </row>

--- a/data/outputs/concept_frequency_consensus.xlsx
+++ b/data/outputs/concept_frequency_consensus.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,145 +454,289 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Cholera Education and Prevention</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Cholera Education and Prevention</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2012</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Diabetes Education and Prevention</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.672</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Diabetes Education and Prevention</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.778</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handing out Medical Supplies </t>
+          <t>Direct Intervention for Cholera Cases</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handing out Medical Supplies </t>
+          <t>Direct Intervention for Cholera Cases</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.412</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>0.526</v>
+        <v>0.3488</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HIV/AIDS Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.07200000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HIV/AIDS Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Infectious Disease Prevention</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Infectious Disease Prevention</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.384</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tuberculosis Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tuberculosis Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.07400000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -629,7 +773,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -641,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -653,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 1}</t>
         </is>
       </c>
     </row>
@@ -665,7 +809,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
         </is>
       </c>
     </row>
@@ -677,7 +821,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 1, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -689,7 +833,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -701,7 +845,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 1, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -713,7 +857,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -725,7 +869,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 1, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -737,7 +881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 1, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -749,7 +893,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -761,7 +905,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 1}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -773,7 +917,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -785,7 +929,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -797,7 +941,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -809,7 +953,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -821,7 +965,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -833,7 +977,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -845,7 +989,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 1, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -857,7 +1001,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 0, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -869,7 +1013,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -881,7 +1025,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -893,7 +1037,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -905,7 +1049,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 0, 'Referrals and Advocacy': 0, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -917,7 +1061,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'CHW Empowered Through Training': 1, 'Referrals and Advocacy': 1, 'Community Empowerment Through Education': 1, 'Handing out Medical Supplies ': 0}</t>
+          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>

--- a/data/outputs/concept_frequency_consensus.xlsx
+++ b/data/outputs/concept_frequency_consensus.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cholera Education and Prevention</t>
+          <t>Bridge Between Community and Health System</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.2739583333333334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cholera Education and Prevention</t>
+          <t>Bridge Between Community and Health System</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002</v>
+        <v>0.2905208333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diabetes Education and Prevention</t>
+          <t>CHW Empowered Through Training</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -499,16 +499,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D4" t="n">
-        <v>0.028</v>
+        <v>0.1607638888888889</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Diabetes Education and Prevention</t>
+          <t>CHW Empowered Through Training</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D5" t="n">
-        <v>0.032</v>
+        <v>0.1486805555555556</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Direct Intervention for Cholera Cases</t>
+          <t>CHW-Led Infectious Disease Management</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.4192708333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Direct Intervention for Cholera Cases</t>
+          <t>CHW-Led Infectious Disease Management</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -553,16 +553,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.4739236111111111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Group Based Health Education</t>
+          <t>Children Served</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -571,16 +571,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>0.342</v>
+        <v>0.3232638888888889</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Group Based Health Education</t>
+          <t>Children Served</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -589,16 +589,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3488</v>
+        <v>0.3462152777777778</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HIV/AIDS Education and Prevention</t>
+          <t>Cholera Education and Prevention</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.06579861111111111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HIV/AIDS Education and Prevention</t>
+          <t>Cholera Education and Prevention</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>0.0720486111111111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Individualized Support and Health Education</t>
+          <t>Clinical Interventions by CHWs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -643,16 +643,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D12" t="n">
-        <v>0.46</v>
+        <v>0.1013888888888889</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Individualized Support and Health Education</t>
+          <t>Clinical Interventions by CHWs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -661,16 +661,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D13" t="n">
-        <v>0.46</v>
+        <v>0.1315277777777778</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infectious Disease Prevention</t>
+          <t>Diabetes Education and Prevention</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D14" t="n">
-        <v>0.42</v>
+        <v>0.02916666666666667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Infectious Disease Prevention</t>
+          <t>Diabetes Education and Prevention</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D15" t="n">
-        <v>0.384</v>
+        <v>0.02013888888888889</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tuberculosis Education and Prevention</t>
+          <t>Direct Clinical Outcomes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -715,28 +715,1180 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D16" t="n">
-        <v>0.052</v>
+        <v>0.1109375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Direct Clinical Outcomes</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>288</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1399305555555556</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Direct Intervention for Cholera Cases</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>288</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.02361111111111111</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Direct Intervention for Cholera Cases</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>288</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.02378472222222222</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>288</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.4295138888888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>288</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4271875</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Drug Abuse: Environment and Awareness</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>288</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.03923611111111111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Drug Abuse: Environment and Awareness</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>288</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0428125</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Elderly Served</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>288</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.01597222222222222</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Elderly Served</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>288</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.015625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>288</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.3128472222222223</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>288</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.2871527777777778</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence (GBV) and Child Protection</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>288</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.09392361111111111</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence (GBV) and Child Protection</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>288</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1134722222222222</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Group Based Health Education</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>288</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3423611111111111</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Group Based Health Education</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>288</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3547569444444444</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HIV/AIDS Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>288</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08680555555555555</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HIV/AIDS Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>288</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1014930555555556</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Handing out Medical Supplies </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>288</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.03802083333333333</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Handing out Medical Supplies </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>288</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08472222222222223</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>288</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.3598958333333334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>288</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.4288541666666667</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>288</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.4717013888888889</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>288</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.5027430555555555</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Infectious Disease Prevention</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>288</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3713541666666667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Infectious Disease Prevention</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>288</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3215277777777777</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lack of Financial Resources for Healthcare</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>288</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.1017361111111111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lack of Financial Resources for Healthcare</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>288</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.1119791666666667</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>288</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.03854166666666667</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>288</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.05416666666666667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>288</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.06041666666666666</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>288</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.06579861111111111</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>288</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.4197916666666667</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>288</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.3461805555555555</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>288</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1545138888888889</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>288</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.1569791666666667</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Education and Challenges</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>288</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.05729166666666666</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Education and Challenges</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>288</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.06232638888888889</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Mental Health Awareness and Support</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>288</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.1697916666666667</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Mental Health Awareness and Support</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>288</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.1540625</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>288</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3098958333333333</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>288</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.3513194444444445</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>288</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.1072916666666667</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>288</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.1431597222222222</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Nutrition Education and Food Access</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>288</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.0859375</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nutrition Education and Food Access</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>288</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.09868055555555556</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Overburdened CHWs</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>288</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.02951388888888889</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Overburdened CHWs</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>288</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.04392361111111111</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>288</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>288</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.5096180555555556</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>288</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.4109375</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>288</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.4565972222222222</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sexual and Reproductive Health Education</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>288</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.1979166666666667</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sexual and Reproductive Health Education</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>288</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.2165277777777778</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Social Isolation or Emotional Distress</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>288</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.1618055555555556</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Social Isolation or Emotional Distress</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>288</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.1619097222222222</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Stigma or Discrimination</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>288</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.13125</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Stigma or Discrimination</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>288</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.1348263888888889</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>288</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.1055555555555556</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>288</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.1730208333333333</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Tuberculosis Education and Prevention</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>288</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.03090277777777778</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Tuberculosis Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>openai</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.07400000000000001</v>
+      <c r="C77" t="n">
+        <v>288</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.0390625</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>288</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.1649305555555556</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>288</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.1800347222222222</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>288</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.4342013888888889</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>288</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.4415972222222223</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +1902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -773,7 +1925,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -785,7 +1937,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -797,7 +1949,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 1}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
         </is>
       </c>
     </row>
@@ -809,7 +1961,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
         </is>
       </c>
     </row>
@@ -821,7 +1973,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -833,7 +1985,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -845,7 +1997,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -857,7 +2009,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -869,7 +2021,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -881,7 +2033,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -893,7 +2045,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -905,7 +2057,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -917,7 +2069,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -929,7 +2081,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -941,7 +2093,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -953,7 +2105,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -965,7 +2117,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 1, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -977,7 +2129,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -989,7 +2141,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 1, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 1, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -1001,7 +2153,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -1013,7 +2165,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -1025,7 +2177,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -1037,7 +2189,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -1049,7 +2201,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
@@ -1061,7 +2213,3163 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CHW Training I take this opportunity to thank our able sister Madam Lilian Dajo for offering opportunity for the training. I also acknowledge Gary Selnow for coming up with this noble project of health information, as a matter of fact. No society or community can stay healthy if they lack health knowledge. May our God bless you all. ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CHW Training I am proud as a CHW because of the knowledge and skills I acquired from the training that has been helping me in the field. I also have a new name in my community. People call me teacher; others call me a doc, which makes my heart jump with joy. The modules and classes were very interesting as were planned from morning to evening the environment for training was conducive. Our trainers Winnie and Kitoli were friendly and lively. They made me enjoy the lessons. They are wonderful, without forgetting humble Lilian for accommodating us and gave us a room for study warm heartedly. KUAP staff are good people to mention. Sister Benedict, Mum Phelgora, who is my role model, Joseph Simiyu, Vincent at the CHIC, Steve and Denis, they are doing a good job. Talking of prevention, I have been sensitizing young mothers and community at large on hygiene, e.g., washing of hands at all times, drinking safe water, and maintaining healthy diet. This has … (I don’t seem to have the rest of the piece.) ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>COVID-19 Many people nowadays are so confused of how things are in today’s world. I met a lady who shocked me with some questions. She asked if COVID-19 can be treated. She said that in their rural area they are to treat COVID-19 by taking herbs. She also added that last week an old granny was cured from COVID-19 after drinking herbs for three consecutive days. She wanted to know whether people living in urban centers may apply the same tactics. I asked her to tell me more about the signs/symptoms that that granny had, and I also taught her of signs/symptoms of COVID-19. I taught her that signs/symptoms may be the same at times, but we can’t tell whether it is malaria or COVID-19 without being tested. I taught her that some bacterial infections which have the same signs/symptoms. She had just mentioned and she agreed with me. ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Malaria I have contracted malaria several times in my life, but the last encounter with malaria was not a beautiful one. I was diagnosed with malaria plus, and the experience was one that you can never want to have, not even in the afterlife. What I hated most about myself that time was the sweat. It smelled so bad that I even hated my body. I lost so much water through sweat, and so I had to use ORS since I was also vomiting and diarrhea-ing. I ate a lot of fruits because I had no appetite and I needed vitamins. My diet consisted of mainly beetroot to help boost my red blood cells because I had jaundice. Uncontrollable headaches was such a bother; I had to also take painkillers. One has to adhere to the malaria drugs for it to be fully treated. Malaria occurs many times. It can come again if prevention measures are not taken like sleeping under the net which is treated or using mosquito repellants. Because I hate malaria so much due to bad experience it brought me and also it caused my cousins death, I usually sleep under treated mosquito net and I always make sure to treat malaria if I am diagnosed with it or anyone so we can prevent death. If a vaccine is developed, I will be the first to take it. ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a life-threatening disease if not well treated or left untreated at all. I have been closely monitoring pregnant women together with the lactating mothers because when pregnant, it is not easy to realize that you are suffering from malaria since the symptoms of malaria and those of early pregnancy are nearly similar. I am saying this because I was once a victim. When I was expecting my first-born baby, I nearly died of malaria thinking that whatever I was feeling or rather suffering from was just symptoms of early pregnancy. I would vomit nearly the whole day eating nothing but water. I felt very weak and my skin turned yellow. I was having a high fever, and I could sweat profoundly during the night. My muscles were paining at the same time. The appetite for food was gone and I could feel much pain in my stomach until one night when I was found lying on the floor, I was taken to the hospital only to realize that my 3-months pregnancy was heavily accompanied with malaria. I was admitted to the hospital for 7 days and I went through series of medical check-ups. After recovering, the doctor advised me never to stay at home whenever I felt the same since it may re-occur. From that day I came to realize that malaria is equally deadly at all ages and repeated attacks of malaria can lead to chronic anemia, malnutrition, and stunted growth. World Health Organization has also recommended malaria vaccine for use in children under the age of 5 living along the lake-side of the country. We as CHW’s are also doing home visitations to ensure there is no ?????? I also advise people to put on protective clothing, have bed nets, and use insecticides like mosquito repellants. I also tell people to take preventive medicine while traveling to a high-risk area before, during, and after their trips. I primarily work with pregnant women, especially first-time mothers. It really pains to lose a soul carrying another soul inside her, I really educate them on how to protect themselves from being attacked, because it becomes very difficult to treat, unlike treating somebody who isn’t expecting. Many people majorly depend on over-the-counter drugs especially when they feel a slight headache. I discourage this because they may not know the kind of parasite that attacked them; hence this is what leads to recurrence of malaria. ---</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>COVID-19 and Nutrition Many people nowadays are practicing nutrition without being followed or monitored. In our locality the elderly and those suffering from chronic diseases and illness are the ones who are mostly adhering to the regulations of boosting their immunity. They do by eating balance diet. I met a guy whom I came in contact with some months ago and was very opposed to the issue of nutrition. He said that there is no need of it and that one can just eat any food for survival. I met him again recently when I was in the field work and told me that he heard news on the TV that old people and those suffering from chronic illness are at a higher risk of contracting COVID-19. He asked for advice on how to stay healthy. I advised him in love, not reminding him of what he said some months ago and was happy. ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 1, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHW Training The recent training that I went through by WiRED International has made it easy for me to understand how COVID-19 affects different people in different ways. Most people in the communities will develop mild to moderate illness and recover without hospitalization. Following the recent reports on COVID-19 ????? 3-4, it shows that Kenya western city of Kisumu has surpassed the capital of Nairobi as having the highest number of confirmed cases which also reported the 1st case of Indian COVID-19 variant. The Indian COVID-19 variant affects many people in Kisumu with a very short period which has also claimed so many lives, more so to those with underlying illnesses. CHW’s have really been pressuring that the communities follow the steps that were laid by the county government of Kisumu—such as social distancing, wearing face masks, washing hands, staying at home while sick and others. ---</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>COVID-19 Kisumu has been experiencing a steady increase in the number of COVID-19 patients in the recent past according to the reports from the Ministry of Health. This has been attributed to the lightened political activities and the easing of restrictions in the areas that were considered as hotspots for the virus, such as the capital Nairobi. Kisumu has also reported the country’s first case of the variant first spotted in India. Due to the escalating numbers, the national government in collaboration with the county government have put strict measures to help stop the spread of the virus. As trained Community Health Workers, we have been in the frontline in helping the government and other stakeholders in implementing these policies. As CHW’s, we have been in the forefront in sensitizing people on the need for frequent hand-washing, wearing of masks properly, sanitizing, and avoiding crowded places. We have also ensured that members of our communities have hand-washing stations within their compounds and in market places. We have also taken the initiative of visiting learning institutions to educate and sensitize students on the need of stopping the spread of COVID-19. As CHW’s, we believe that learners and students are a proper link between CHW’s and the community. They can easily pass that information back to the society. Another step that we have taken is to visit the elderly and the people with underlying health conditions to sensitize them on the vaccination against COVID-19. This we are doing by informing them about the benefits that come with the jab. We also encourage other members of the community to get the jab. Through this sensitization effort, we have seen the society embracing change, and we hope to see a steady decline in the COVID-19 numbers that are reported from Kisumu. ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 1, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>COVID-19 COVID-19 has been a stampede in our country. It has affected people around the globe, both developed and third world countries, Kenya being among them. The first case in our country was announced in February 2020 in the city of Nairobi. The spread was rapid all over the counties and the most affected counties were Nairobi and Mombasa. The virus spread in many counties and now in Kisumu. In Kisumu, the virus spread like bush fire that forced the authorities to come up with the containment measures like curfew, which in one point has affected people’s welfare. It has affected business. This has forced people not to carry out business at night, thus led to loss of steady income. Places of worship have been shut down and this affected people spiritually. COVID-19 pandemic has affected Kisumu economically in that some businesses have been closed, people displaced from their working places, some losing their jobs and going back to their native homes to start from square one. As a Community Health Worker, following the WHO directives, I protect myself first. I make sure that I wear a mask, before and after the task. I sanitize. I create awareness on COVID-19 by teaching people what COVID-19 is, how it spreads, signs and symptoms, then preventive measures like wearing masks, washing hands at all times, avoiding over crowded places and also maintaining social distancing. I also taught the community that when one is feeling sick and has COVID-19 signs and symptoms, they should stay at home and to stop roaming around while monitoring the symptoms by drinking a lot of water, eating a balanced diet, practicing steam inhaling and body exercises. If symptoms persist, they should seek medical assistance. I walked door-to-door and in public places doing these things and it has brought a great impact to many people of Kisumu. Cases of diarrhea have dropped, because of the hand-washing hygiene. People are watching what they eat by eating balanced diets to boost their immune systems and also by exercising. Those who are adhering to these directives are safe from contracting COVID-19 and many infectious diseases and are also grateful. ---</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>COVID-19 The current status of COVID-19 in Kisumu has increased recording the highest number of COVID-19 cases, and at a positivity rate of 11 percent. Inspection numbers increased barely a week after Kisumu hosted the 58th Madaraka Day celebrations that saw thousands of people gather around Jommo Kenyatta International Stadium to catch a glimpse of the celebration, many them not adhering to public health directives. Some of the attendees of the event including journalists went to self-isolation. Many hospitals in the region are full of COVID-19 patients and others in isolation, with the experts warning that if the measures are not strictly adhered to then the region could be the next epicenter of the disease in the country. Many people have also died. It has increased up to the community level and various schools. With many people being sent back home, a few take only days and die because the home-based care cannot support their conditions. Insufficient beds, ICU, oxygen and PPE’s to support COVID-19 patients. Also less personnel led to overwhelming of work and that has contributed so any deaths in the hospital. Many die not attended to, ten deaths are counted every day. The hospitals are not accommodating people with other diseases because the COVID-19 patients are the ones being attended to due to lack of space. Many people are also dying because they cannot afford a private hospital because they are too expensive. For example, in many of the private hospitals, a bed a night goes for almost 100,000 and some even go for 300,000 a night. Most families are forced to search for oxygen for their people, some to an extent of physically fighting over the oxygen. If a sick neighbor is discharged or dies, they run to grab as seen in a footage shown by a certain local media station. Many groups are not adhering to COVID-19 protocols, e.g., the bodaboda, the matatu, hotels, bar and restaurant owners. Most business groups, the local alcohol brewers and sellers. Political gatherings at funerals and some public events. This has led to the increase of COVID-19 as mentioned before. This has led to the government issuing certain directives like the 72 hours burial if a person dies. In that case, the government has set rules to curb the spread of COVID-19 in Kisumu county. Curfew starting from 7 p.m. to 4 a.m., which I think is not helping a lot because people still gather at local clubs during the day. Closure of all gatherings for 30 days, arrest of those not following the protocols like not putting on the face masks are charged in court, transect walk by the government officials, administration and regular police plus the area chiefs to assess the situation in the areas. (???). Many people have lost their jobs due to the closure of most premises. As compared to last year, cases of school dropouts due to lack of school fees because most parents lost their jobs. Shortage of the vaccine has also been witnessed as a small percentage got vaccinated. As a CHW, I have been creating door-to-door awareness. I have also conducted health education to students and pupils on COVID-19. I have also conducted education to women groups and men. I have created awareness to chiefs office. I’ve worked with public health officers to fumigate informal settlements, gathering places within informal settlements. Distribute hand sanitizer and liquid soap. But that is not enough because we cannot reach everyone due to scarcity of materials. We have distributed IEC materials with COVID-19 messages and washing stations. The changes I have seen so far is that most people I have seen are practicing the proper washing of hands, putting on masks and social distancing. Due to health education and awareness creation, there are behavior changes on children in various schools by putting on masks. Schools have also put washing stations in different places from the entrance. Markets within the informal settlements, people are practicing social distance. Continuous door-to-door awareness also goes on. My experience during this COVID-19 has been sympathetic. Reaching out to the community has been a lifetime blessing. My hope for tomorrow is to see a world full of true love and humanity. ---</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>COVID-19 The COVID-19 pandemic has seen some of the Kisumu residents lose their jobs due to closure of some work places or cut off some employees and many yet have had a rough time maintaining their businesses especially. With the curfew at 7 p.m., those with businesses, especially those in the good businesses, have seen losses. Many families have also lost their loved ones due to corona virus and as a result. As a Community Health Worker, I have created awareness of the COVID-19 pandemic and the most obvious symptoms and how to prevent contacting the virus through educating the residents in my community how to wash their hands with soap and clean running water, and how to use sanitizer and maintaining social distance and avoiding crowded places because it’s not easy to tell one who has the virus, and I have also distributed masks and some few hand rub sanitizers and educating them on how to wear and dispose of the mask after use and how to wear a mask properly. ---</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>COVID-19 COVID-19 affects different people in different ways. Most infected people will develop mild to moderate illness and recover without hospitalization. Most common symptoms are fever, dry cough, and tiredness. Other symptoms are aches and pains, sore throat, diarrhea, conjunctivitis, headache, loss of taste or smell, and a rash on skin or discoloration of fingers or toes. We also have serious symptoms like difficulty breathing or shortness of breath, chest pain or pressure, and loss of speech or movement. In Kisumu, we have COVID-19 but the percentage of the virus was not very high. In some weeks back, it was found that some Indians shipped in, being that there was no total lock down. It was said that they were possessing COVID-19 and therefore intermingling took place in different parts causing our people to get more infections. In addition, they also came with another new COVID-19 named the Indian corona virus variant, which is more dangerous than the South Africa variant or the British variant which we have been dealing with. When we had Madaraka Day in Kisumu, we know very well that we received different people from different places. There was no social distance in some areas and some people were also not wearing their masks totally. The behaviors at long last led to the spread of the virus, hence increase of the infection to our people. But in real sense, we had the virus even before the holiday and the celebration itself. Life has been so tough, being that there is inadequate hospitals and oxygen supply leading to high death rate. Therefore, it is always better to prevent before you cure. We are advised to observe social distance, wear masks properly and wash your hands with soap and running water for at least twenty seconds and more. As a Community Health Worker, I encourage all these to minimize infecting of other people and also to reduce the number of infected people. I also tell people to avoid gatherings in different places and to observe hygiene at all times. Being that the churches are closed, it doesn’t mean that prayers have also been stopped, but it is the building which has been closed and therefore we can always have prayers in our houses but with few people. I also pray that may the Lord have mercy on us, forgive us our sins, and save us from this pandemic. ---</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Water Treatment It is the process of removing undesirable chemical, biological, contaminants, suspended solids and gases from water. Water can be contaminated because of flooding and poor sanitary conditions. In a certain village there was cholera and typhoid each and every time, leading people to hospital to get treatment. When I asked them if they normally treat water, they told me that they did not have money to buy water-guard. I told them that it is not a must to use water-guard, but we have cheap processes to use like boiling to sixty minutes, and exposing water to the sun to kill dangerous agents in water. All these will prevent you from diarrhea, typhoid, and cholera. From that point, when I got back to check for them, I was very happy to see them living a very happy life and also maintaining cleanliness. ---</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Drug Abuse/Addiction In the community, I came about some people who were misusing drugs and now they became addicted and were unable to control. Such drugs were like heroin, cocaine, and alcohol. I managed to talk to them and advised them concerning the bad effects which they could undergo. The drug that may be addictive target your brain’s reward system. They flood your brain with a chemical called dopamine. With time, your brain gets used to extra dopamine, so you might need to take more of the drug to get the same good feeling. Therefore, other things you enjoyed like food and hanging out with family may give you less pleasure. When you use drugs for a long time, it can cause changes in other brain chemical systems and circuits as well, hence can hurt your judgement, decision-making, memory, and ability to learn, hence making you to have bad health. ---</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Malaria As a victim, I also had malaria. My experience was not a good one. I first had mild symptoms which was a headache in which I self-treated myself with over-the-counter drugs. I started having severe signs and symptoms a few days later which were diarrhea, vomiting, and joint pains. I was rushed to the nearest medical center in which I was tested and found that I had a severe malaria and would have probably died if I wasn’t taken to the medical center for immediate medical care. I was rushed to a ward and given a shot of quinine drip and placed on a drip because of dehydration. I was hospitalized for three days at the ward being monitored on how I feel and whether I felt any discomfort on my body. In which my response was that I only felt and had a headache. After finishing my 3 days at the medical center, I was prescribed with a malaria drug by a doctor in which I took it for 3 days, twice a day, to improve my condition. After 3 days of following the doctors advises and precaution, my body was functioning normally again. ---</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a serious and sometimes fatal disease caused by a parasite that commonly infects a female anopheles mosquito which feeds on humans. Having malaria is a bad experience ever. Physical symptoms, that is high fever, can make one to lose red blood cells which may cause anemia. Other symptoms like nausea, vomiting, and diarrhea may also occur and make one to lose a lot of water. Fever and flu-like illness including shaking chills, headache, muscle aches, and tiredness. Malaria may also cause jaundice if not promptly treated. The infections can become severe and cause kidney failure, seizures, coma and death. Sincerely speaking before I became a CHW when I felt like malaria symptoms coming, I used to go over-the-counter and buy malaria drugs, of which I realized after being a CHW was not a good idea. Malaria can return time and again because if not completing the full dose of malaria drugs. Not only completing dose but also we don’t get rid of mosquitos’ breeding places and sleeping under a treated mosquito net. As a CHW, what I can do to help people with malaria is to advise them to visit health facilities for proper check-up to determine whether it is malaria or not, because some diseases have similar symptoms as malaria, e.g., influenza. I also advise them that when they have confirmed to have malaria, they have to complete their doses to avoid recurrence of malaria and also to avoid drug abuse. I heard of two children who died from malaria. Their over-the-counter which did not go well with them, at the time they were taken to the hospital it was too late for they didn’t make it. As a CHW in my dealing with malaria, I advise people and myself to clear mosquitoes breeding sites, e.g., clearing bushes, removal of stagnant water, and to cover ???? water, using or sleeping under treated mosquito nets, and that they should go for malaria check-ups whenever they experience the symptoms and to avoid over-the-counter drugs. ---</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease caused by a parasite called plasmodium parasite, transmitted by the bite of infected Anopheles mosquitos. Malaria spreads by animal or insect bites or stings and by blood products (unclean needles or unscreened blood). The physical symptoms are like fever, vomiting, headache, yellow skin, diarrhea, fatigue, kidney failure, seizure/confusion, sweating, muscle aches, chest pain, chills that shake the whole body, dizziness and severe symptoms such as paralysis. Therefore, in any case I feel these symptoms, some of them, not all because I may not go through all of the symptoms. Why? It may happen from time to time. It is advisable that the moment it starts, I will force myself to go to the hospital for a check-up because that is the right place for me to get treatment. Hence, it will also help me to avoid it to become severe. Malaria even treated can re-occur again and again, so it is good to take action immediately before danger. I do advise people with malaria symptoms to go for a test before taking any painkiller, because this can cause danger. I also take an action by taking some of them in hospitals so that they can get treatment. I assure them to finish the malaria dose and treatment to avoid it from reoccurring again after a short time. On the prevention side part of it, I avoid mosquito bites by using insect repellent, hence tell the community to do net. You also have to wear long-sleeved clothing and long pants if you are outdoors at night. For pregnant mothers, I tell them to go for check-up whenever they feel the symptoms because malaria affects her and the fetus. It can lead to maternal anemia, fetal loss, premature delivery, and delivery of low birth weight infants. So many people have died because of malaria and what causes this is ignorance. Some of the patients ignore the symptoms and also take wrong medication before tests, leading to severe infections hence death. It is good to love yourself, love and protect your life because it is given once by our creator who is God. Observe cleanliness at all cost to prevent more infections from occurring. ---</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy It was on Thursday 10th that I met a young girl who was sitting under bulaboda shade when I was at ???? I moved closer to her and we had one-on-one talk with her. Due to her condition she was stressed up because she was pregnant and the family was very bitter and ??? at her ??? a long talk with her. I took my time to go and talk to her mother. Though the mother was disappointed, I managed to talk to her and she accepted her daughter back and promised that she would take care of the baby as her daughter will be going back to school to sit for her final exams. ---</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Child Malnutrition The world is experiencing a lot of challenges like high inflation due to COVID-19 pandemic and the latest war in Russia and Ukraine. Kenya is not left behind as the cost of living is very high due to shortage of food. I came across a three-year-old baby who was very thin. I suspected that the child might be sick, but to my assessment I found out from the mother that the child was not getting enough food. I instructed her to make sure what she feeds the child is rich with all the nutrients, as this would help the child grow stronger and healthier. I also referred the mother to the Obimga Nutrition Center for further assessment. Am happy that the child has shown improvement since he started feeding on the food which the mother was instructed to prepare for the child. ---</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cholera Our communities, though industrialized, still get affected with cholera. The reason why we still suffer from cholera is because of the industrialization that is still taking place. While the government is busy building roads and other things, they do not take caution on water pipes, and therefore when there is a breakage anywhere along the lines, our water becomes contaminated and it is through this contamination that our community members get infected with cholera. Though this cholera is not a big threat in our community, it still affects some parts of our community. I taught my audience on how to treat their drinking water using the solar disinfection and also to wash their hands clean to prevent them from contracting cholera. ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence As I was doing my routine follow-up, I happened to come across a young mother who was undergoing mental toucher. She shared with me her story. She has three children (all girls) aged between 9 and sixteen years. He husband is always drunk and has decided to marry off the 16-year-old girl and this had brought a lot of fight in their family as to whether the girl ought to be married off. The mother is opposed to the practice, because she has attended a talk on gender-based violence and is convinced that even if the daughter wants to go through the right of marriage, they should make the decision when they are older enough, that is 18 years and above. The mother urged me and the entire team to continue the good work that we have started, as it is going to help so many young people on the decision they make. ---</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Drug Abuse/Addiction I had a session with young men aged 15-23 years where we discussed about drug abuse. My findings are that drug abuse is still rampant among young people. This is attributed to peer influence and easy accessibility of the drugs. Most interestingly, they don’t have a specific drug that they are using. They mix all of them. The most common drugs that they use include ?????, cigarettes, alcohol, and cocaine. These drugs are readily available and accessible. Most of them are not aware of the consequences both short and long term. During our discussion, I made them understand the risks and consequences of using the drugs. Proper sensitization is still needed to enable them to have adequate information about dangers of drugs. ---</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Drug Abuse/Addiction I visited a home that is located in Mowlem community. Met a woman and her children and talked about drug abuse and other diseases such as malaria and COVID-19. But the main topic we talked about was drug abuse. This is because of her current experience. The mother shared out that her husband is an alcoholic and drug addict (marijuana). She also shared out that her husband is violent towards her and doesn’t support her and the children. I advised her to report the matter to authorities or NGO’s that deal with gender-based violence and to see how they can help her and the children. I also advised her if she can try to suggest to her husband and rehabilitation in which I explained the meaning and benefits. The woman said she will try to speak with her husband and if things don’t change she will seek help from NGO’s which can help her financial, emotional, mental, and physical health. ---</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Drug Abuse/Addiction There is a lot of talk about drugs and substance abuse in the community, on the street, at school, on Internet, and also on television. Some of these talks are true, some are not. As I was teaching about drugs, I realized that much of what people hear about drugs actually comes from those selling them. Reformed drug dealers have confessed that they would have said anything to get others to buy drugs. I do tell my teens not to be fooled. They need facts to avoid becoming hooked on drugs. That is why WiRED International has prepared a program for them to have a better understanding of all types of drugs, their benefits, and their side effects. The most common feedback I normally get after my classes is that people take drugs because they want to change something in their lives. They think drugs are a solution. But eventually the drugs become the problem. ---</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hypertension Those who suffer from hypertension go through a tough time in their lives. It is now that I understand why we in our ghetto usually say that there are rich people’s diseases. Rich people’s diseases are like the diabetes hypertension and those other incurable diseases. For instance, there is this woman whom I talked to, she was suffering from hypertension. This woman was not a rich person but she had to manage the disease. She had to take medications which she complains are very expensive, and she also complained about the storage of the meds. She said the drugs needed a fridge and she had none. She was crying that if we as WiRED community can introduce something like a bank where medicines are stored with particular names, one can just to take her medicine and go on with their daily work, then she would die happily. ---</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Infertility Infertility is a major problem in the community. Some women are accused by their spouses to be infertile because people believe men cannot be infertile. Others say that some infertility causes are caused by contraceptives such as pills and family planning method which is Depo. Women say Depo has really affected them as they have problems in balancing their hormones with their menses. According to most women, they prefer implant for 3 years while for 5 years they prefer a woman who has at least 3 kids to use it because of the side effects. Another family planning method that has complication as stated is the use of coil because a certain lady use it but still got pregnant. Therefore, most women prefer implant as the best method for family planning because it does to not lead to infertility cases. ---</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence Gender violence covers all forms of violence that have to do with socially constructed behaviors. These can include violence against men, such as abuse of boys by men, abuse of men by women, and abuse of women by men. Violence against women refers only to women. It is frequently confused with gender violence because over ninety percent of violence is violence against women. Violence is often used in the family situation as a weapon of power. Women are often in the subordinate position. Therefore, they are the ones who suffer violence and do so in silence. This can either be physical, sexual, or psychological. There are some cases of men being subjected to domestic violence, but these are far and a few. Majority of ???? However, gender-based violence does not only occur within the family situation. In criminal cases, where the offender is convicted and the punishment is corporal. It can only be administered on men and not women. Thanks to WiRED for offering us a training. I am happy that now as a CHW after the WiRED training, I can now teach my community of their rights and the procedure to follow on gender-based violence and am happy that they are getting help from the places where we direct them. ---</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>High Blood Pressure Many people nowadays still don’t understand more about blood pressure. Some say that people with obesity are the ones that are at risk of getting such a condition. They do deny that slender people cannot get/have high blood pressure. I shared with them that anyone is at risk of getting high blood pressure. I shared with them that people’s life style can put them at risk of getting high blood pressure—e.g., eating junk food, not doing physical exercise like walking, running, or jogging. Too much consumption of alcohol or any drug which is not prescribed by a doctor. I shared with them about the prevention and treatment. They were so grateful and promised to change. ---</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>HIV Prevention This month, when I was giving health education on HIV prevention measures, I came across so many commercial sex workers who were rally in need of preventive materials such as condoms, but they were unable to get enough since there is insufficient commodities in the country. I managed to teach them about the importance of using pre-exposure prophylaxis, that is PREPs, for those that were saying they are HIV negative. I taught them that PREP is highly effective at preventing HIV when taken as indicated and that it reduces the risk of getting HIV from sex by about 90% when taken as prescribed. I also encouraged them to be going for clinical check-ups for at least 3 times in a year in order for them to be sure of their status and be prevented from also contracting STIs which may later destroy their reproductive systems. ---</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene It has been a long holiday and I have been meeting with the group of girls and boys who have reached the age of adolescence and some are almost. In our normal talks I found out that most of them do not have the right information about menstrual hygiene. So I started informing them about its importance and how to manage it. As we all know that it is the act of collecting or absorbing of the overflowing blood into your underwear. You may not feel well and it looks so scary to see blood in your underwear, but it is so natural and normal. To manage this situation you should use pads. Cotton wool, reusable pads or a piece of cloth. When using pads you unwrap the pads from the package and stick it on your underwear. Same to cotton wool; you roll and place it on your underwear, and those using reusable pads and piece of cloth do not place too big cloth; just take a normal size and place it safely. After some hours you change the pads and piece of cloth etc. Don’t use the pads for a long time because it gets so soaked it causes rashes on your skin and movement won’t be easy. Dispose of the pads safely. Wrap them with tissue and dip into pit. And the reusable pads to be washed with soap and water and dry in the sun. They were happy and thankful for the information. ---</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Mumps As I was going round and sensitizing people about health issues, I realized that many people had mumps. I came across a household consisting of a mother and her three children who were infected and affected by mumps. They had not gone to the hospital for treatment as they believed that mumps are just bad omen and will disappear with time even without any treatment. The mother told me that their religion does not allow them to go to the hospital for further diagnosis and treatment and so they had to wait for the mumps to disappear by their own. I took my time and counseled both the mother and her children, who were 13 years, 15 years, and 17 years. I told them that it’s good if they are referred for further diagnosis and treatment at the health facility. They agreed to go to the hospital of their own choice. I gave them the referral letter and they went to Limumba Health Center for further treatment.. After 3 days a follow-up was done and I found them doing well. They were very happy and grateful for the education I gave them. They told me to continue educating people in the community as some community members rely so much on religion more than anything else. They thanked me and promised to go to the hospital in case of any health problem. ---</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chicken Pox As I have been going around as a CHW giving health education to the community members I came across a household where all the children had chicken pox and the mother was not willing to take the children to the facility for further treatment. I counseled the mother on the benefit of visiting the facility and taking her kids to the facility but still the mother was not willing to take her kids to the facility. I did several counseling and mentioning to the mother that the way she is not serious with the health problems of her children she might end up losing her kids. After several counseling to the mother she agreed to take her kids to the facility for further treatment. After two days when I did followup to that household I found out that the mother and her kids were doing so well and the mother promised not to behave the way that she did since the life of her kids was very important. ---</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Mental Health During the month of January I kicked off my outreach at Gonda and came across an issue when discussing the topic of mental health. During this topic I realized this young girl was withdrawn all of a sudden. After discussing the types of mental illness I realized that she was not okay with the topic. I however finished the topic and diverted to the topic on stress. I called her aside after the session and we talked one on one and she opened up on her situation at home. She recently lost her mother and was still undergoing the grief stage. She is a student in St. Ignatius Sec. School and currently staying with her aunt, who is not okay with her performance. She explained to me that she never talked to anyone about her situation. She cannot concentrate well in class whenever her mind rings on her mother’s death. I had a therapy talk together with a counselor whom I referred to help her. She is now undergoing her sessions with her counselor during the weekends. She is now trying to cope with situation both at home and at school. ---</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Malaria I’m Lency Mmbone Mahindu, a community health worker at Nyalenda Slums. As I was doing my daily routine at my community, I came across one family alongside river Wigwa who were suffering of malaria and did not go to the hospital nor look for what was bringing about the sickness that was on and off. As a community health worker we came together and discussed causes of malaria and what can make the sickness to be recurring every now and then. We found out that the members were not sleeping under mosquito nets and their compound was also actually making the breeding of mosquitos too be many. While discussing, we can across the challenges that they explained that sleeping under mosquito net was making them uncomfortable and others said that sleeping under nets makes their chest to be congested being they are not used to it. Being I’m a health educator, I explained to them the benefits of sleeping under mosquito net and clearing the bushes that are around us, and they were very happy to know that they’ve been getting sick every now and then and they had a solution but did not know. I referred them to the hospital. I came back to check on my clients to see if they went to the hospital and cleared the bushes and I found out that they did everything as we discussed and they were now living healthy and happy. ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Vaccination Vaccination boosts immune system. I met a mother of two children. She asked me the importance of vaccination. I told her that vaccination prevents individuals from infections of diseases, e.g. small pox, measles, TB &amp; polio. I also assured her that these diseases kill. I advised her to do so and make sure that she doesn’t even miss one so that she can live a happy life with good health. Eventually she told me that all about vaccination is true and agreed to do so. She also came to know that proper vaccination and breast-feeding can lead to fight against any disease that may encounter the body. ---</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>HIV Despite every trial to reduce HIV prevalence in our communities it is still there and many people will contact new infections daily. Good news is that so many people have learned to embrace their status and have learned to live with it. However there are those who still haven’t decided that they will live with the disease for the rest of their lives. These are the people who die from stigma. Since they can’t agree that they have this disease they have decided to change their way of living by hiding and not going for medicines and refusing to disclose their status leading to untimely deaths. I talked to some youths about this and I hope this will be spread in the community to help prevent these deaths. ---</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Communicable and Uncommunicable Disease I had a session with community members on communicable and uncommunicable disease. The session was an active session. The members had their opinions on the diseases which were witchcraft and many others. I didn’t hinder their opinions. I also gave them the effects and importance of knowing communicable and uncommunicable diseases. The community had a positive attitude on the session. The importance that I had shared with the community was to know how to treat the disease, to know the preventive, measures, to know the signs and symptoms, and many others. The effect that I had shared with the community was it may cause death. It may cause health effects like fever and headache. The solution that I had shared with the community was to seek medical attention to a professional medical assistant. ---</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cold and Flu It has been cold in Kisumu for the past one month. Many people have been infected with colds and they tend to mistake them with the flu. Though the symptoms might be the same flu and cold are different diseases. Flu can be treated with antibiotics but it is most deadlier than common cold. Flu affects the lungs, nose and throat. ---</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Diarrhea Many children are suffering from diarrhea due to the carelessness of their mothers. I have been taking mothers and caregivers through some measures that can help stop the spread, such as washing hands frequently using good hand washing techniques. I always advise most household members who are experiencing that not to visit places such as swimming pools until they get better and also to take their babies to be vaccinated against rotovirus. I also advise families that a sudden change in diet can result in diarrhea. Spicy foods such as those containing chillies can give some people diarrhea. Some medical treatments may cause diarrhea as a side effect e.g. antibiotics. I teach all these in the community so as to do away with so many cases of diarrhea. ---</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Water Treatment Water treatment has been the main practice done in the community mainly because water is mostly used at home and for drinking. A number of people use water guard to treat water for drinking and some boil water for drinking thus this reduces contamination of diseases such as typhoid and stomach ache to individuals. Awareness has been the main key. This encourages a lot of people to avoid risks. The government has been a great help because the KIWASCO supplies treated water from their company thus when the water passes through water catchment areas less harm is being encountered. Water treatment has reduced typhoid cases and stomach ache health related issues. ---</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Basics of Health Educating community on the basics of health has helped a lot in the communities we serve a s CHWs. People are getting to know of various disease outbreaks, how fast they can spread, the causes and even preventive measures they are supposed to carry out without waiting for a CHW to come in. Nowadays mothers understand the benefits of immunizations to their young ones. Before they used to take their children to routine clinics up to 2 years. Since after they are well educated I can see at least up to 85% of mothers in slums taking their children for vitamin A supplements and weight monitoring, deworming and any clinical requirements for children older than 2 years, which is good feedback to me as a CHW and I surely know that things will remain the same and we will continue with the good work we had started. ---</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Meningitis In my area while on duty I came across a person who was looking sick and tired. I talked to her and in our conversations I noticed that she had the symptoms of meningitis. Meningitis is an inflammation; a swelling of the protective membrane covering the brain and spinal cord. It’s a bacterial or viral infection of the fluid surrounding the brain and spinal cord that usually causes the swelling. The symptoms she had were headache, fever, looking sick, and stiff neck. I advised her to visit the nearest facility as soon as possible because of the serious symptoms. Meningitis is serious disease and causes convulsions mostly in children, and can kill if necessary measures are not observed. She was thankful and promised to take all the medications given and by maintaining healthy habits like getting plenty of rest and drinking plenty of water. ---</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Hypertension The frequent creation of awareness that CHW has been creating in the community has led to reduction in the number of people affected by hypertension disease. We have been advocating for lifestyle changes which include weight loss, increased physical activities and dietary changes in individuals and also moderation of alcohol and a diet that is high in consumption of fruit, vegetables, and low fat dairy products. Community outreaches also motivates our people a lot and should be conducted regularly in the future for early detection oof hypertension cases and proper health education about high blood pressure and its dangerous consequences. All the efforts made will make our community a free hypertension zone. ---</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Water Treatment Many people use untreated water that they don’t know is untreated. We have a distributor called KIWASCO that provides clean water to our community members. The water is believed to be clean because it comes from a reliable water company that serves the whole of Kisumu county including government hospitals and government offices. The truth is that these people give us clean water but along the way before reaching the consumer there are bursts that end up mixing with dirty water and even sewage at some point. In that we end up getting contaminated water. Cholera is so rampant and this is due to this ignorance so in the field I taught my community members that they should treat water no matter where thy draw it from so as to prevent them from getting waterborne diseases. ---</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Child Abuse Family relatives. If a parent is found guilty of abuse he/she will go under rehabilitation. In such a case they will get custody of their child back. Ultimately the goal is to uphold the family unit while protecting the child’s interests and well-being. However, cohesion initiatives such as the “nyumba kuni “ initiative can bridge this gap. If for instance a child goes missing the whole neighborhood will be involved in looking for the child. This kind of unity can be achieved even without calamity and create socially friendly communities for our children to grow up in which can physically, emotionally, social and create economic empowerment for our future leaders, our today’s children. ---</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Hypertension Many thought that only overweight and oversize people are at higher risk of getting heart attack due to high blood pressure, which is not the case. Our participants were of the same view but we managed to sensitize them to the contrary. Heart attack can occur due to various things such as stress and unstable state of mind. We informed our participants to regularly check their blood pressure so that in case of any problem they can get medical attention as soon as possible. We also advised them to check on their diet because some of the food that we eat can lead to obesity hence making someone vulnerable to high blood pressure. ---</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hypertension; HIV/AIDS I created awareness on blood pressure, HIV/AIDS, Malaria, and many other diseases. I had a session with a group on blood pressure and mostly HIV/AIDS. I encouraged the audience on knowing their blood pressure and HIV/AIDS status. We talked about the effects of blood pressure and HIV/AIDS. On blood pressure we talked on how to maintain the normal blood pressure by exercising and eating nutritious food. And also talked about the causes of high blood pressure, which are overweight, not doing enough exercise, and many others. On the HIV/AIDS we talked about the effects of the disease and the importance of learning your status. We had discussed the causes which were having unprotected sex and many others and how to treat the disease which was to take the ARV drugs. I made sure to tell them that HIV/AIDS does not have a cure. The session was positive and the audience participated well. ---</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Tuberculosis My success story of March began in Manyatia, in my area, Corner Mbaya. I was in one of my outreach teaching to a group of young men and women. We started discussing about tuberculosis, which has been a menace in our community for a long time. It has been believed to be a horrific disease in the olden days. We clearly talked about the symptoms and signs such as extreme night sweats, persistent chest pain, coughing out blood, unintended weight loss and even reduced playfulness in children . My audience clearly understood the signs and symptoms and the need of being screened if they have persistent coughs. One of the participants in the audience gave her story of how her grandmother was once diagnosed with TB last year. Her diagnosis led to one of her grandchildren found to be infected with the same disease. Luckily one of the CHW in her area was doing her health talk, and realized they needed to be referred to the nearest health facility. Most of the community members started to see. After a long treatment of both grandmother and the child, the TB was treated and the household was free from the disease. This also helped in raising awareness of the TB in the community. This story caught our attention during the topic and some people in the community still view TB as a bad and outrageous disease. At the end of the session the audience understood the prevention measures in regard to TB. They also understood that TB can be treated. ---</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 1, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Nutrition As I was going round in the community and sensitizing the community members about nutrition, I found out that some community members are now aware of utilizing the locally available foods, while others are still selling some foods to buy other food varieties. In the community malnutrition cases are still cropping in as a result of lack of awareness. As I was creating awareness on nutrition a lady told me that she has been selling eggs to buy mandazis. I informed her that eggs contain protein so instead of selling eggs, she can just cook the eggs and add some green vegetables and ugaly.. She can also add some pawpaws as they were locally available in her farmyard. The lady was so happy and told me she would do what I informed her to do. She was also providing strong tea to her child who is below five years. I told her to give her porridge from a locally prepared flour containing four food groups. The lady was very happy and promised to continue feeding the children a healthy diet containing all the required nutrients that helps in growth and development. The whole community are now happy about nutrition sensitization. ---</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Screening As I was doing my daily work as a Community Health Volunteer I came across a certain woman who had two children in Obunga Community, who were always having coughs and runny noses on and off, the said she had different types of medications and none had worked. On 24th March we had an outreach in Obunga Slums on which we were doing different types of medications because we had doctors with us. We started with blood pressure, weight, height, and then we send you to the doctor for further consultation and to be given mediation. I mobilized the woman who was always in hospital to treat her children. She came with her kids and they talked to our doctor and she was given some medications for the kids and she was even doubting if the medicine would work because she had gone through a lot with her kids. On Wednesday as I was doing my follow-ups to every person that I mobilized to go for treatment during our outreach in Obunga. I came across the woman who had two kids and she was very happy to report that she was doing well with her kids; that her children had healed and she confessed that she had never seen that medicine that she was given called Zeditone, and that now she realized that what the kids were suffering from was allergy and she really appreciated for her kids are well and she can now live a normal life like others. Thanks to WiRED for bringing smiles to the community. ---</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene As I was going around in my community educating health related issues to the people I came across a young girl about the age of 14 was in the initial stage of experiencing body changes at the adolescent stage. I selected a young girl almost her age to discuss menstrual hygiene. The girl had a bad attitude towards using sanitary pads because her mother had instructed her in using small pieces of cloth during her menses because they were poor and they could not afford to buy pads. After completing the sessions I urged her to stay back so as to understand her situation better. After talking to her I provided her with a pack of sanitary napkins. ---</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nutrition and Kitchen Gardens This month I found it important to teach my community the importance of having a kitchen garden during the rainy season. My aim was to improve community health, expand nutritional awareness, bring communities closer together, reduce crime e.g. theft, and produce more fruits and vegetables for local food banks. The people who I taught this idea of kitchen garden are very happy since it occupies a small plot size, located close to the homestead, having diversity of crops and easily adaptable by the poor with limited resources. The available fruits also helps boost the immune system of their children who has low immunity due to consistent use of antibiotic in cases of certain diseases such as cough. ---</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Polio Many people in the community call polio a curse from ancestors. Some even say that it is a sin that happened with the parents long time ago that is coming back to the child. A case happened of a child who had polio. He had been sick for a very long time which led him to sit on a wheelchair because of lack of knowledge. Nobody told the parent of the child that at early stages polio is treatable and there is also a vaccine for polio. When I taught them about polio she cried and shouted and asked me why we did not teach them early enough. She said if we did then her child would not have died. Most people said her child had died because of witchcraft, which was not even true. ---</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 1, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Typhoid, Cholera and Bilharzia The community at the moment are experiencing floods due to the rainy season. According to some people there is a year of typhoid, cholera and bilharzia because of the flooded areas. Recently cholera has been a threat as some cases have been reported, thus awareness has been created and people advised to wash their hands frequently. Someone raised an alarm with the current availability of snails; thus it is a threat because of the everyday rains. The community have been advised not to walk barefooted when it is rainy because they can easily be contaminated with typhoid, cholera and bilharzia. ---</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Tuberculosis This is a contagious infection that usually attacks the lungs. It can also spread to other body parts like brain and spine. It is caused by a mycobacterium tuberculosis. Tuberculosis has symptoms like cough that lasts more than 3 weeks, chest pain, coughing up blood, feeling tired all the time, night sweats, chills, fever, loss of appetite, and weight loss. Tuberculosis is an airborne disease and so it can be spread through air just like cold or flu. You can get tuberculosis if you come into contact with people who have it, but how? When someone who has TB coughs, sneezes, talks, laughs, or sings they release tiny droplets that contain the germs. If you breathe in these germs you can get it. Therefore I advised my clients to take action of going to the hospital whenever they come across these signs and symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cholera There have been cases of cholera reported in certain parts of Kisumu over the last one month. Our focus has been on the sensitization of the community on preventive measures. These cases have been caused by the heavy downpour. Hand washing has been found to be the most common way of preventing cholera. We also urged our community members to regularly eat clean food and maintain high levels of hygiene. Cholera is a disease which can cause death within a short period of time and therefore it’s necessary to seek medical attention as soon as you notice its symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cholera During the month of April I learned a lot in my field work. It’s the month which the country experienced a lot of downpour after a long season of drought. Many households within my working area got into a lot of challenges. As a result of floods, high cost of living has led to many families lack to get food to feed their families as well as having safe drinking water. Due to these problems, some families in the informal settlement in Kisumu resorted to tap dam water for their domestic use. The dam water is not safe if not well heated for drinking because it is collected from the rusted iron roofs which has been still for so long. For these reasons, cholera was pronounced an outbreak in Kisumu, in particular in Nyalonda and Ibonga slums. As a trained CHW who performs his mandate in training the community 24 hours a week it was very critical time for me to conduct as many sessions as I could to sensitize members of the community to take precaution measures to prevent themselves from the outbreak. I managed to share with them the WiRED cholera module and after sharing many of the participants were very happy for learning new preventive measures against cholera and promised to practice it every day. Success story to my work as a CHW, last but not least, I want to confirm that our work has contributed a lot in the prevention of cholera because not any deaths from the killer disease was reported and now the outbreak has been fully contained and well managed. ---</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 1, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Cholera It is a bacterial disease and it is spread through contaminated water. It causes diarrhea and dehydration. Risk of cholera epidemic is highest when poverty, war or natural disasters force people to live in crowded conditions without adequate solutions. I advised my clients to always make sure that the water they use must be very clean, drinking water more so should be boiled or you can use water guard too purify the water. Fruits and vegetables should be washed before they are eaten. If you maintain these you should be free from diarrhea and stomachache. ---</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Malaria During my community work at my community in Nialenda slums Wigwa area I came across certain households who were really affected with malaria due to the rainy season that we are having at this moment. The area is densely populated and very busy making the mosquitos to multiply more and cause malaria being these households don’t have enough mosquito nets to cover all of them and they are also torn, too. As a community health worker, I had to educate them in the importance of cleaning the bushes and covering the dirty water that are around them to keep the mosquitos away and avoid malaria in our community. After being educated they cleared all the bushes and became safe in controlling malaria. ---</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cholera During the month of April, I met a group of young girls of around ages of 9-14 years. We had a discussion about cholera which was the major outbreak in Kisumu, especially Nyalenda, Nyalenda, Nyamasama and Manyatta. We discussed the various ways of the spread of the disease such as drinking untreated water and defecating feces near water bodies. The girls got interested in the hand washing procedure to help with stopping the spread of cholera. We went through hand washing steps and also hand rub with sanitizer, and the group learned to differentiate the two (hand rub and hand wash). I managed to raise awareness of cholera and also taught them signs and symptoms when a person has contacted the disease. They also learned that cholera could kill a person within a span of 24 hours and hence need to seek medical attention immediately as possible. That outreach was a success with one of the many groups I accomplished in the month of April. ---</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Malaria As I was going around in the community and sensitizing people about malaria disease I found out that malaria is a very big threat in the community as a whole. People in the community were suffering a lot as malaria prevalence in the community was very high. Most people neglected the preventive measures of malaria which included slushing of bushes around houses, draining of stagnant waters, closing the doors and windows early enough in the evening, sleeping under treated mosquito nets, taking of SP for the pregnant mothers, application of mosquito repellants on our bodies, pouring used oils on stagnant water to kill larva, putting on long pants and long sleeves to cover our bodies, putting screens on windows and doors to prevent mosquitos from entering the houses, practice indoor residual spraying once a year, and for those traveling in malaria endemic areas to take anti-malarial tablets to prevent them being infected with malaria. The community members were very happy and were ready to go and practice all that as concerns the prevention measures of malaria. One member also added one point that says that avoid germs and waste which acts as the breeding sites for mosquitos. Malaria is no longer a threat to the community. ---</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Diarrhea As I was doing my daily to daily activity of community sensitization in different villages like in Burdami, Kunyamudha and Kombedu, I came across a caregiver who had a child who has diarrhea. I talked with the mother concerning the diarrhea, counseled her and talked to her on the benefit of taking the child to the hospital. She agreed and I wrote her a referral letter and she agreed to take her child to the hospital. The following day as I was doing health education at the household level I met with the mother of the baby who had diarrhea and she confirmed to me that her baby was now doing well after taking her to the hospital and receiving some treatment. ---</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sexual Violence I was on the field on 7/4/2023 where I organized a health discussion with a group of 25 females who I engaged with and came out with the following issues/concerns. We deeply discussed about rape cases and the steps to take in case they fell victim. For instance one girl came out as a rape victim. She was raped some time back. We discussed the issue as a group and learned that the first step is to report to the police station then proceed to the hospital within 24 hours of the horrific ordeal. I encouraged and advised the girls not to fall victim of men who tend to lure them with cheap goodies as gifts and false promises. ---</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Parenting During the month of June, as I was doing my outreach in Manyatta I came across a group of young men and women. During the outreach it was a period of celebrating the day of the African child. Due to the theme of the celebration, the rights of the child in this technological era, we talked about phone and television as a way of exposing our children to the technological world. We discussed issues such as child trafficking and violations such as defilement and harassment. We discussed together that children should be monitored and parental guidance should be observed. Parents giving phones to their children should also monitor what their children watch on the phones to avoid bad exposure to the child. Parents should also monitor the kinds of things their children watch on TV. The discussion led us to understanding more of the children we handle basically from toddler to adolescent age. We also talked about GBV. ---</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STIs and UTIs As I was doing my daily health talk to my community in Nyalenda Dums, I came across a group of women who were really complaining that their private parts were always itching them after they were treated with many drugs (Kienyej) but didn’t have any trust. The session was all about STI and UTI and their eyes opened and they learned about the types of UTI which are caused by sharing toilets with the infected people and not practicing hygiene and that several transmitted infections are caused by having unprotected sex with infected people. After a long discussion with them, I advised them to seek medication, and afterwards practice prevention and good hygiene against their diseases. During my follow-up in the community, I found my clients happy and could now tell the difference between UTI and STI and they were so empowered that they became champions of prevention. ---</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Flu Flu is a common viral infection that can be serious on high risk groups. There has been an outbreak of flu within Kisumu town that has caused severe illness on people. Residents have confused it and thought that it is COVID 19. During this reporting period we concentrated on educating our communities about flu. Flu attacks the lungs, nose, and throat, with children and older adults being at higher risk. We told our communities to treat flu as soon as they notice they symptoms to avoid complications. ---</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Breast Cancer As I was working in the field I met a young lady who had a lump on the breast and it was producing pus. She said that she thought it was just a boil that didn’t bother her, and that she would just squeeze it and it would go away. What caught my attention was that this thing she said that it started out as a pimple and it kept growing over the year and now it became a painful lump and she was wanting to squeeze it all out once she had time. I did not believe that this was just a boil. I told her to go for free cancer screening and now she was diagnosed with breast cancer and is admitted for treatment. She says the treatment is very painful but she is enduring. ---</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Self-Esteem As I was going around and sensitizing the community about health issues, I introduced a topic on self-esteem. The members were very happy to discuss about self-esteem and know more about it. There are people with low self-esteem and some have high self-esteem. The ones with low self-esteem are always shy, not able to speak in front of people easily irritated and cannot explain fully what they are and their potentiality as a person. Such people are being encouraged to stand strongly on their own, know who they want to be and gain courage to talk publicly in public places so as to be strong enough. One participant stood and told the gathering that she has been having low self-esteem since she was born. This resulted when her mother passed away at her tender age around four years old and the step mother used to quarrel her a lot in front of people. This affected her so much but since she has got some information, she’s going to change and needed a referral. She was referred to a professional counselor and when doing follow up, I found that she’s now doing well. She’s so appreciative for this program and thanks them a lot. She promised to be attending educational gatherings. ---</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Flu There has been an outbreak whereby people are coughing, sneezing, experiencing flu and headache frequently. To some people they say COVID 19 because of the symptoms but to some it is said that it is influenza ‘A’ which comes with severe symptoms unlike influenza ‘B’ with mild symptoms. Most people are not sure of the current symptoms thus the good thing is that when one experiences such symptoms they go to the hospital for treatment. There is a plot where everyone was coughing and having flu. I realized the houses are closer and this makes it easier for everyone to experience the same because the ventilation space is not good. ---</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 1, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Anemia Many people, especially children, suffer from anemia. It is caused by blood loss, when the body fails to make red blood cells even when the red cells die faster than they are created. The most common type of anemia is the iron deficiency anemia. This happens when one loses a lot of iron from the body because iron creates hemoglobin. When we are experiencing our monthly periods we lose a lot of blood and iron. During childbirth the same happens, therefore I had to take my audience through the module to teach them the foods that help in replacement of iron every time they lose blood. Foods rich in iron should be taken at all times to help build up iron in the blood so that in case one loses blood in one way or another they cannot suffer from anemia. ---</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Misinformation about Ulcers There is a rumor that goes around in our locality that when one has stomach ache the high chance is that it’s the sign and symptoms of ulcers. Another rumor is that thin people are more likely to be affected with ulcers because of too much stress. I told them that those are just myths. I taught them that anybody is at risk of getting ulcers due to one’s lifestyle and can determine if one can stay healthy or not. I taught them about the treatment, preventative measures and also the causes. They were very happy and promise to keep safe. ---</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training Working as a CHW has given me a different name in the community and I had a good time with different people. Some refer to me as a doctor; a teacher. Some kids I was as a mother to them. I interacted with different age groups and had their views on the issues of health and social life. ---</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Mental Health On this issue of mental health has been a random effect on many of the families; more on younger. I talked to some of them and many are affected by stigmatism. This has severely affected youths and is very concerning. You find that someone is going through a certain difficulty but he/she can’t share or seek help being that this will bring discrimination among their people. I had to talk and council them on this then we agreed that we should challenge stigma and provide understanding and compassion towards those struggling with mental health issues. ---</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Drug Abuse This has been rampant in the community among the youths. Mostly it is an influence from where we live, gather and those we mingle with. Many young girls and boys are abusing drugs and when you ask them, they said the surroundings they are living and some of their parents are selling these drugs thus it has been an addiction to their lives. I came to realize this and some of them are ready to change and be good products to the community. I will continue advising the youths to stop abusing drugs by counseling them every time I have the opportunity. ---</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Pregnancy When I was doing my daily to daily health education to the village of Bandani, Kombedo and Konyaneclha, I came across a teenage girl who was 4 months pregnant. She was vomiting a lot and she was also feeling some headaches, and she was opting to go to the pharmacy to buy some drugs to stop the vomiting and also to reduce the headache she was feeling. I took her aside after the session, talked to her, and educated her on the benefits of ANC and the disadvantages of buying drugs from the pharmacy. She agreed to start AHC as soon as possible and also agreed not to buy drugs from the pharmacy. I referred her to the nearest health facility, known as Airport Health Center, where she was given AHC book and she also got several AHC services and she was written for the return date on when she will go back for another visit of which it will be by next month July 30, 2013. The girl was really grateful for the support she got from the health center. ---</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Child Abuse Child abuse can be either subjecting children to physical, emotional or psychological conditions that violate their rights as envisioned in the Children’s Act. If any person has knowledge of that, they should be obliged to take measures to protect the interests of the child. Existing reporting lines include the police, children’s office, local authorities (chiefs and assistant chiefs) as well as any other government office that deals with children’s welfare. After reporting a case of child abuse the relevant authorities will take up the matter of investigation, and if evidence is found then further steps are taken. The perpetrator(s) will be arrested and arraigned in a court of law for legal action, and the child taken to foster care or placed with alternative caregivers. ---</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Hand Washing I visited different places and talked to people about hand hygiene. We discussed the good effects of hand hygiene and did some practicals. It was so good and they enjoyed the process. Though they require the soap and detergents for hand washing. I try to advise them on this so that every time they wash their hands. Family Planning I met young women who were using different types of family planning and the disadvantages of them. So I advised them to seek medical on what they are experiencing so that they are told on what is good with their hormones. Some agreed to do so and they will visit medical facility. ---</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Depression I met a young mother of two and she was also breastfeeding. Her health was deteriorating. I wanted to know where the problem was. She told me that she is passing through tough times and she wanted help. I came to realize that she was depressed. I taught her about the signs and symptoms of the condition. I advised her how to manage the sickness and she was so happy. We talked out large and she told me that she was planning to commit suicide. She told me that if it were not for the advice that I shared with her she could die. She promised to adhere with the rules and regulations that I shared with her. She was so grateful. ---</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Dysentery In my usual work as a community health volunteer, I came across a certain lady alongside Wigwa area in Nyalenda. The lady was sick and tired because she had blood coming out of her private part and she didn’t know the cause. So while I was doing my normal education I talked about dysentery and how it affects people. The lady talked about her health issues and was very emotional, so I counseled her and taught her different types of diseases that are being caused by water that is contaminated. After a long duration I referred the girl at Jootch, where she was treated and given some medication that really helped her. ---</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Flu The month of June has not been easy. Kisumu Country has experienced an outbreak of influenza. This has been seen as another wave of COVID 19. Within the informal settlement where I was, many people including churches, schools, and public places had left putting up hand washing equipment. And most of the people have left washing their hands as they used to during COVID 19 pandemic. Through this habit, many people including children got influenza infection and it has not been easy for these people to get treatment as a result of high cost of living in the country. Quite a number of people are not able to pay. ---</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Flu As a community health worker I got myself too into this situation whereby I got infected by the influenza virus. It has not been so easy to heal very fast, because the influenza drugs are a bit expensive. Having gone through this situation I took my time to educate and remind my community about the benefits of continuous hand washing. After thorough awareness creation I’m able to witness people washing their hands and also putting up hand washing equipment. Thanks to me is a very promising story. ---</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Family Planning and Pregnancy Had a session with a teenage girl on pregnancy and family planning. The girl shared out that has been active sexually and been using family planning. The girl shared out that she thinks she’s pregnant and she had been using family planning and seek on advice on how she got pregnant and yet she had put family planning. I shared out that the family planning had been ineffective, expired, or that she had been sexually active during the seven days that she was not to be sexually active so as the family planning was to be effective in which she positively participated. I also advised that if she think she’s pregnant she should go to the nearest clinic and seek professional advice on how to take care of herself if she’s pregnant. And if not she should also check on herself on which family planning she should use to avoid unexpectedly early pregnancy. ---</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training This is my personal story that I would wish to share. Having trained by WiRED International as a community health worker, I have had a lot of experiences that have not only transformed me, but the entire community and my family at large. My work in the community has elevated me to many county of Kisumu platforms where through the county department of health have accorded me recognition and also given me many invites to their outreach activities to offer my skills as a CHW. Just recently I got an invitation for a five day training about community health committees. I attended the training. The modules are very detailed and easy to understand. Something that made the participants very happy. I am very happy to say that after the training I was chosen to be the chairman of the community health committee (CHC) of Obimga Dispensary where I am heading a group. All this has happened because of the training I received from WiRED International. I give thanks to WiRED International team, the CEO and board of directives for bringing this good training to us in Kisumu Kenya. It is my prayer that more will come for instruction. ---</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Depression During my community sensitization and health talk education at Luala Village, I came across a mother of three who was going through serious depression. She told me that her husband has neglected her with her children, and got married to another woman. The three children were sent home from school fees and has stayed at home for the whole of last term. As I was having one on one with her she agreed to go and visit a counsellor wand also start her small business to help her support her 3 kids. I referred her to a professional counsellor and during my follow up I found her doing well psychotically and economically. ---</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Malaria and Pregnancy During the month of August as I was doing my daily outreach I noticed one in the audience looking timid. I was doing a door to door outreach to Kasawa Community. She was 34 years of age and she was also in her first trimester of her pregnancy. She is married and this will be her second baby. She had chills and was complaining of headaches too. After assessing the symptoms I had to refer the woman to the nearest facility, Crislela, a local facility. She was willing and ready to be escorted. I escorted her to the facility and she was well taken care of with the doctor. She was diagnosed with malaria and her pregnancy was also monitored. ---</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STIs As I was walking in different villages educating the community members on the topic of STI’s, I came across a young mother and some two men who really wanted to talk to me privately concerning the topic. After the topic of the discussion, we went and sat separately aside whereby these community members confessed that they have been having problems concerning their private parts. They talked about some signs and symptoms they were facing. I talked to them, counseled them and then I referred them to the nearest center, which was Airport AHC. After some 3 days when I did follow-ups I found out that they have been served well at the facility. The clients really appreciated the services that they received. ---</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Good menstrual hygiene management plays a key role in enabling women and girls to reach their full potential. The challenges that menstruating girls and women face encompasses more than a basic lack of supplies or infrastructure. While menstruation is normal and healthy part of life for most women and girls, in our community/society the experience continues to be affected by cultural taboos and discriminatory social norms. I realized that lack of information about menstrual hygiene leads to unhygienic and unhealthy menstrual practices that create misconceptions and negative attitudes which motivates shaming, bullying, and even gender based violence. Most of the schools lack adequate water, sanitation and hygiene services crucial to enable girls and female teachers to manage menstrual hygiene. ---</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Arthritis In the community while performing my daily duties I came across a person who had difficulty in walking. He had pain in one side of the leg. As a CHW I convinced him and took time to talk to him. So in our conversation I found out he had symptoms of arthritis, so I asked him if he knew what arthritis is. Unfortunately he didn’t know, so I informed him that it is an infection caused by a fault in the immune system that causes the body to attack its own tissue in the immune system or by metabolic condition such as gout. And the symptoms are pain in the joint, stiffness of leg, or feeling numb. If anyone notices the symptoms they should rush to the facility to see a doctor for consultation. You can also manage the situation by doing exercises. ---</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STIs and HIV/AIDS As I was working in the community many people, more so youths, are experiencing a lot and have to be taught on the awareness of these diseases. We talked and discussed various ways of preventing the STIs and the HIV/AIDS that our people are living within the community that they are afraid to disclose so they can be helped. I urged the youths to avoid the rampant sexual intercourse because if they have to they should protect themselves but the best is to abstain. Peer pressure has been leading our girls to this act and they suffer a lot. To the ones we discussed with agreed to seek medical check-ups so that they live to know their futures. Many youths are urging me to keep on educating these effects in the community so that they may learn a lot and make their lives better for a future living. ---</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Mumps In our society there are a lot of misconceptions and myths about some kind of diseases, e.g., mumps. They said that when one has mumps he or she has been bewitched or cursed. They also said that the only treatment is for one to rotate an oak tree for three times. I taught them that mumps are caused by a virus that passes from one person to another through saliva, nasal secretions, and also personal contact. It is the swelling of the salivary glands that makes the cheeks to swell. I shared with them about the symptoms, prevention, and treatment as well. The child who had been already infected, I advised the mother to give him plenty of fluids to avoid dehydration due to fever, and to seek medical check-up as well. ---</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Family Planning So many women are partaking in family planning methods and the most loved the implant. Many people have different reactions to the method they prefer most. It is more preferable because it’s longer than the other forms of hormonal forms of family planning. For instance I met a certain lady in the field that had problem with her menstrual periods. She menstruated for a whole month and now she was becoming thin because of the constant bleeding. She used all types of meds to stop the bleeding but the bleeding did not stop and it was now becoming a disease. I told her to remove the implant and use a not hormonal type of family planning. She said she is trying to find a hospital to remove it. ---</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>HIV/AIDS During my mentorship in the community I came across a certain group in my community in Nyalenda Dums who were very vulnerable and were at risk of contracting HIV/AIDS because they didn’t know the difference between PEP, PREP, and condom. During our discussions, they were very happy to know that PEP is pre-exposure prophylaxis which is used to treat/help those people who have been raped, or pricked with sharp objects or the ones that have been involved in an accident, to prevent them from contracting HIV and it’s taken 72 hours after the incident and it’s taken for 28 days and you adhere. And also we talked about PREP which they knew it was taken after engaging in unprotected sex, so I tried to empower them that PREP is taken by HIV negative people who are at risk of contracting HIV being that they don’t trust each other, or taken by those who are married to HIV positive people that we call them discordant partners, and it’s taken 7 days before engaging in sex and it is taken daily as long as you’re at risk. Only stop after the risk is not there. We also talked about condoms which they know that it could be reused which was wrong and we discussed that condom is only used once and no reusing and is used to prevent you from getting HIV, STI’s and pregnancy During my follow-ups my people were very happy to be empowered and no longer at risk of getting HIV, STI’s and other diseases. ---</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence Many women who are married suffer a lot in their marriages. They undergo a lot of gender-based violence and keep on keeping quiet about it. They fear losing their spouses and children, hence cannot come out to be helped. In my field work I came about such cases whereby I referred some of them to the facilities but some are still in denial state. On my side I also managed to counsel some of them in which they are in a good state now and they always give me thanks for helping them, making me be happy. What I came to realize is that most of married people need to be empowered because some still believe in fighting, not knowing that it can’t work at all and cannot even solve problems. It can only work when you find where the problem is and analyze, sit down, calm yourself, and talk when you are not angry, leading to solving the problem. ---</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Water Treatment and Typhoid When I was going round in the community sensitizing them on water borne diseases, I came across a man who has been using contaminated water due to breakages of water pipes as a result of heavy downfalls. He had serious symptoms of vomiting and stomach upsets. I referred him to the health center where he was diagnosed with typhoid disease. He was treated and given some drugs home. When I went back to do follow up, I found him doing well and gave him information on how to prevent and control all the water borne diseases. He agreed to ever use boiled or treated water for drinking and always wash fruits with running water before eating them. He was thankful for what the organization is doing by providing information and knowledge to the community as a whole. ---</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Basics of Health Educating the community on the basics of health has helped a lot in the communities we serve as CHWs. People are getting to know of various disease outbreaks, how fast they can spread, the causes and even preventive measures. Nowadays mothers understand the benefit of immunization to their young ones. Before they used to take their children to routine clinics up to 1 year. Since after they are well educated, I can see up to 80% of mothers in slums taking their children for vitamin A supplements and weight monitoring deworming and any clinical requirements for children older than 2 years, which is a good feedback to me as a CHW, and I surely know that this will remain the same and will continue. ---</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Depression I met a young woman who was suffering from depression. This is because she became a mother in a very tender age. She is nineteen years now and she is a mother of three. She said that she doesn’t know the meaning of being alive because she is suffering so much. She said that the man who made her pregnant when she was only fourteen years of age decided to abandon her because she was illiterate. She met another man who took her in wither child and she gave birth to two more children. The so called husband decided to leave her for another woman. He doesn’t take care of the children anymore. The burden is too heavy for her to bear and she wanted to end her life and the life of the children. I talked to her at length and came in an agreement. She said that she is so grateful for the advice and promised not to take her life and the life of the kids. ---</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Pneumonia I realized that many people still do not understand the causes of pneumonia. Most community members will tell you that it is caused by too much cold and when asked the symptoms they don’t clearly know what signs to check before concluding it is pneumonia. This month I came across a child who has had a cough for more than seven days and the mother was just giving the child the normal drugs for cough. I assessed the child and found that the child was suffering from pneumonia and immediately I referred the child to the nearest health facility. The child was admitted for a week there. After she was discharged I continued educating the mother on the causes, signs and symptoms and also preventive measures to take so that the same doesn’t repeat itself next time. The mother was very grateful for the kind of assessment I did and promised to be more careful when observing the child. ---</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Family Planning and Pregnancy I had a session with a teenage girl on pregnancy and family planning. The girl shared out that she has been active sexually and been using family planning. The girl shared out that she thinks she’s pregnant and she had been using family planning and seek advice on how she got pregnant and yet she had put family planning. I shared out that the family planning had been ineffective/expired or she had been sexually active within the seven days that she was not to be sexually active so as the family planning was to be effective, in which she positively participated. I also advised if she thinks she’s pregnant she should go to the nearest clinic and seek professional advice on how to take care of herself if she’s pregnant. And if not she should also check on herself on which family planning she should use to avoid unexpectedly early pregnancy. ---</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Tuberculosis As I was doing my day to day health education to my respective areas the Kombedo, Bandani, and Kanyanyamedha, I came across this young gentleman who said that he wanted to talk privately. Then after I had sone with my health education we went aside with the young man where he told me that he has been taking TB drugs but he defaulted and he really wanted to be helped before it worsens. I talked to him, counseled Himont the importance of adherence, and also talked to him about the importance of VCT. After all that counseling I referred him to the nearest health facility for further check-ups. After 2 days when I was doing follow-up to the client, I found out that the. Young man. Was given drugs. For TB and he was also tested for HIV. The client was grateful for the information and referral. ---</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Mental Health In the month of November I was doing my random community health outreach. I managed to meet a group of young mothers who were breastfeeding. We managed to talk about mental health and as we were deeply immersing in the topic I realized that most of them have had childhood traumatic events and traumatic marital issues. One of the participants seemed withdrawn when we started talking about signs and symptoms of mental ill health. She explained of how her childhood life was; she was orphaned at the age of 13 years and was forced to live from one relative to another. This life wasn’t good at all because most of the relatives were not friendly as she thought. This led to her teenage pregnancy and what followed was early marriage. She explained on how she went on PSS (psychological social support) by one of the CBO’s in the community. She was linked with up a paralegal and was linked to PSS group which consisted of 7 young women like her. She ended motivating the other young women who are going under some traumatic events. ---</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Waterborne Diseases When I was working in the community I found out that there is a lot of diseases brought by waterborne diseases such as dysentery. Many are using water from the boreholes and are not treated as required; thus many are complaining about stomach aches. I had informed them the importance of using safe water by boiling and using chlorine. However much the economy is high they have to be careful with these diseases so that they can prevent it. There is a lot of drainages that had been flowing all over the community. Many youths are very happy to get education on drug abuse where they are ready not to involve in these groups of bad company. I am urging them to be good youths so that they can have a good behavior in the community. ---</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Diarrhea During my internship in the community in educating them on health education I came across a family that were really diarrheaing because they took Kienyeji during the night. In the morning they started diarrheaing so I educated them on hygiene and they narrated that they didn’t wash the vegetables very well with much water. So they agreed that they’ll always wash vegetables with a lot of water and also fruits. They’ll maintain good hygiene to make them safe during these rains that floods that cause a lot of sickness and needs maintenance. ---</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Scabies In the field I met a woman who was ill suffering from scabies. She had suffered for quite a long time and had not known it was only a skin condition. She was afraid that she had suffered from HIV/AIDS and was afraid of testing and she was waiting for her death because of stigma. The skin condition was now worse than it should have been. I advised her to go to a hospital. She went to the hospital to cure her skin condition but she came back and told me that the hospital was so expensive she could not afford. We thought about a solution and we came up with a decision of using natural remedies to help cure her skin condition. She has tried it and it is going well. It is better than it was before, and she is thanking me so much. ---</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training The training that was offered by WiRED was a great opportunity for me to learn and explore different health issues affecting my community. I believe I can now help educate my community about issues related to health. My becoming the link between the community and our healthcare facility is very beneficial. Teaching my community about important health issues that affect our lives will bring positive change. ---</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training The CHWs training really changed my life. It helped me to stand before people and talk with confidence because I was well trained with important information for my community. Also, our teachers modeled how to elicit and handle personal and difficult questions sensitively. I appreciate having had this opportunity to learn how to help people who might be shy like me. ---</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training The facilitators were so detailed in giving information and knowledge concerning health education. The environment was conducive to learning. The meals were good and appreciated. Time management by the staff and facilitators was good. ---</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training The WiRED training was so extensive that I now feel empowered. Beforehand, I didn’t know about different types of diseases. Because of a lack of information, I didn’t understand the causes of illnesses in our bodies. Being empowered has made me a different person, and I am eager to implement my knowledge in my community. ---</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training Before the WiRED CHW training, I was naive about health issues. Since the training, I know better how to approach my community with basic information. I can now help my community members understand the myths and misconceptions about such topics as menstrual health and hygiene. I am grateful to be a trained CHW because now I am able to help and support my community. ---</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training Thanks to the WiRED training, I am well equipped with health knowledge and can help confront health issues in my community as they arise. This training has helped me know how to prevent various diseases. I have been taught how to help our community members with knowledge so that they can help themselves, too. ---</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training The CHW training was very educational. The facilitators were well prepared and very knowledgeable. I am now well equipped to go back to the community and implement what I have been taught. I’m happy that I am a well-trained CHW, who can deliver helpful information and teach other members of my community about health issues. ---</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training The CHW training helped enlighten me in so many ways. I know now that there are many health issues that can be managed early on, just through giving health education to people. The trainers were very good in teaching the information. They took us through diseases, causes, prevention and also gave us skills on how to handle the population. These skills will help us teach basic knowledge to our communities and precautions regarding current emerging health issues. I am very grateful to the entire WiRED team for this wonderful opportunity. I truly believe that I can now make a greater, more positive change in my community. ---</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training The CHW training helped me a lot. Now I know how to use various medical tools like blood pressure machines and thermometers to screen members of my community. I now have knowledge of first aid, which I can apply confidently to the public. ---</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>WiRED CHW Training First, I am so humbled. The training was so meaningful to me. I learned a lot and feel I can now empower the community. Through this training, I learned about different types of diseases I encounter nowadays and their management. But most importantly, I learned how to cooperate with youths and others in the community to give them helpful information. I would love to continue with more WiRED trainings, so that I can acquire more knowledge about health issues and better relate to people in the community. ---</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Fibroids It has come to our attention that a number of women are experiencing fibroids and have different perspectives about its existence. Upon sharing with some women, it seems that they think it (fibroids) comes about with the family planning methods which are being used. Some women say it is due to the delay of giving birth and it blocks the fallopian tubes. Whereas some say it comes about because of family history. Awareness should be created to educate more women about treatment and measures to take to control. ---</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 1, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Chronic Illness As I was going round in the community and sensitizing (educating) them on health-related issues, I came across a man who claimed to feeling weak, tired, and dizzy most of the time. He said that he sweats a lot, mostly at night. I took the initiative and tested his sugar level using a glucometer. He was experiencing diabetes. I then referred him to the health centre for more diagnosis. He went to the hospital and was diagnosed with diabetes and put on drugs. He is now doing well and happy for the support he has received. He appreciates and thanks the Wired team for the implementation of this project in the community. ---</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Malaria During my mentorship in my community in Nyalenda slums, I came across a certain household who were always suffering from Malaria off and on, which became a routine for them to visit the hospital nearly every week. As a community health worker, I had to probe more and come up with a solution for them to live a healthy life. I educated them on the importance of sleeping under treated mosquito nets every day and night, slashing all bushes, covering all water vessels, and boreholds to keep them from suffering again from malaria. During my usual follow-ups, the family was very healthy and really thanked me the education. ---</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Mental Health During this mobilization, I have met with different health issues, mostly mental health. This affects most youths and adults. There has been a lot of negligence in the community, people are taking the laws into their own hands. Mental disorders have caused a lot (of concern) in the community. Many youths are taking their own lives or dealing with depression that leads to early deaths. I had to discuss with them how they can live productively in the community with their families, friends and even with their negligence. I had to discuss with them about First Aids. Mostly about situations that occurred in our homes and even around them, such as Burns, Bleedings and Accidents. I explained to them how they can handle some situations in if they come across someone in need. What they should do and how to reach the necessary people or facility. This has been promised to be in consideration. ---</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Infectious Diseases Examples: measles and chickenpox. Infectious diseases are those diseases which are caused by micro-organisms. These are: fungi e.g. mushroom, bacteria, protozoa, and viruses. These micro-organisms are seen by the use of a microscope because of their tininess. In the community, there were some patients who had these infectious diseases. The bad thing they were doing was going to the chemist to access drugs not knowing what they were suffering from. I advised them to always seek treatment from the hospital. We also discussed how infectious diseases entered our bodies: inhalation of airborne germs: when people breathe, sneeze (laugh), ingestion of contaminated food, possible cholera and typhoid, human/animal contact, kissing of infected persons, skin contact with infected persons, ticks/mosquito bites. We also discussed some of the signs &amp; symptoms like fever, fatigue, and diarrhea. ---</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Ulcers In the community where we live people suffer from ulcers but pretend that it is heartburn. When I was giving a health talk, I came across a client who was prone to cigarettes. He had ulcers and there form I told him to avoid cigarettes because it added negatively to his health, making him unwell. For good treatment, I referred him to Migusi hospital for checkups. He was treated well. He also ended up doing away with smoking, making his life and health even better. To make it much better, he had a friend who he taught and he also became a good person in the community. This made me become very happy indeed. ---</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Depression During my field work training and health (talk) sensitization, I came across a family headed by a mother of five, who was going through severe depression. In our discussions, she shared with me that she a husband whom she loved so much but sue to hard economic times, her husband lost his job and could not attend to the household needs anymore. As a result of this situation, the husband ran away and left her with the children. She had school going children, as two of them were to join this year. The remaining one, was to report back to school after Christmas holidays. They were sent back home for not paying school fees and had to stay at home. In one of our discussions, I advised her to visit a professional counselor, which she accepted to do so. I also encouraged her to start a small business to enable her to support her children. Since I knew one of the counselors at Amani Counseling Centre, I referred her there. Through my follow-ups, I have found out that she is doing so well. The church gave some money to start a business. She is selling boiled and roasted maize cobs at the Obunga Junction and through this she has been able to return her children to school. ---</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Malaria I conducted door-to-door visit and came to meet a woman of about 31 years old. She was pregnant with her fourth child. She is married. The woman had chills and complained of a headache. Through assessing her symptoms, I came to suspect that she could have malaria and referred her to the nearest medical facility (Obunga Dispensary). She was eager to go, I therefore gave her company to the facility. The nurses took her blood samples to the laboratories. Her blood test came out positive for malaria. She was referred to the doctor who gave her treatment as well as receiving monitoring her pregnancy. As a community health worker, I always get happy whenever the people I refer (from my area of operation) get treatment. ---</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Tuberculosis As I was educating my community members on tuberculosis: how one can contact Tb, preventive measures, and how one can go about seeking help it he or she has contacted Tb. I had finished giving health education, there was a certain young man who approached me told me how he was feeling. First, he told me that he sweats a lot at night, coughs a lot, and from November of last year, his weight has reduced dramatically. I talked to him, counselled him and then I referred him to the nearest health facility, which was Airport health center. After 3 days, when I did my follow-up, I found out that the gentleman was screened for Tb. The results came out the he had Tb. He was then counselled again and given Tb drugs. ---</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Dislocation A young woman was running from the police officers. She slipped and fell down. She assumed that she was okay, but after two days her right leg starting swelling. I met her yesterday and the situation was worsening. She could not move her leg as quick as she used to do. I told her to visit a health facility as quick as possible. She promised to do so because the pain was severe. I told her maybe it could be a dislocation but she has to go to the health facility. ---</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>First Aid I found it important to promote recovery and how to prevent further injuries in the community after going through the first aid modules. I am an ambassador in my community, teaching members of the community the importance of giving first aid. I gave them various methods on how to quickly provide first aid whenever there is an incident that requires quick attendance. This education makes them capable of managing incidents and also allows them to take care of children’s injuries promptly. Performing first aid helps reduce the child’s recovery time. It can also save them from a temporary disability turning into a permanent one. I appreciate Wired Internation for coming up with this kind of training and for choosing the best trainers for us. ---</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Red-eye disease There is a disease that has surfaced in Kenya known as the red-eye disease. Though this disease has not yet been traced to Kisumu, it is said to be in the coastal regions. It is communicable is you use an infected persons eyeglasses. You are at risk of contracting the disease. It is said that the eye swells, turns red with an itchy discharge. Those people who are on the coast have been told to observe hygiene such as: washing hands with soap and water, using had sanitizers, and avoiding sharing eye glasses and personal belongings. As CHWs, we are on the alert, in case it reaches our region. We now know how to help prevent it in our community. ---</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Gender-based Violence During my health talk in Obunga area, I came across one woman who has always been maltreated/assaulted by her husband mostly. She opened up to me ow her husband has been beating her and been locking her inside to avoid contact with her neighbors or anybody, until she fully recovers. I told her to find a way to report the matter to any nearby recognized authority since she might end up being killed one day. ---</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Obunga Health Outreach/Health Screening Clinic Obunga is one of the three major unplanned settlements in Kisumu-Kenya and ranks highest in lack of proper infrastructure access to clean water, social and health amenities. It has a population of 5000 people living in about 1000 to 1500 households. Obunga is divided into 5 units, Obunga control 1, control 2, Kasarani, Seqaseqa, and Mbita. All five units only have a poorly equipped local dispensary which is managed by the county government of Kisumu. With health as a major priority of the residents, Wired Community Health Workers, based in the area insist that health outreach be done at least once a month. Yet, this is not always possible since other areas also need to be covered. Based on the above, outreaches in Obunga are always packed. Community Health Workers always have extra work in controlling the crowds of patients who scramble for the services. Obunga Control One outreach: As always, the Community Health Workers, make sure that the tent, with one hundred chairs are immediately in place after sunrise, since the clients always start trooping in as early as 8:00 am. Our team comprises of a clinical officer. 9:00 am, the tent is already full but the crowd is well managed by the Community Health Workers, clad in their yellow and green T-shirts with their tags on as always. Lillian, the coordinator is there to instruct. The services offered are the treatment of minor ailments like Malaria, TB screening with a special X-ray machine ( USAID sponsored), blood pressure check-up, blood sugar check-up, HIV testing services. The Community Health Workers also provide health education under the slogan “Community Health (supports) with Knowledge. All the services are absolutely free. What stood out: A young boy, about ___ years old was escorted into the camp by Zachary, one of the 5 health workers, who stated that he found him lying helpless in a house where he lived with his elderly grandma. The old woman had always depended on the well wishes of others for support for both herself and the grandson, whose mother had passed on, narrated Zachary. The boy had a serious skin and ear infection. With the help of the Health workers, the boy was taken through the system, proper examination and management was done, and he went back home with the right drugs. Gratitude to Wired for giving a helping hand. ---</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 1, 'Women Served': 0, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 1, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Cholera During the month of April, as I was doing my daily outreach in my community, I came across one young girl who was 16 years old. She seemed to be a little overweight for her age. Her legs were swollen. On approaching and questioning her, she responded that she was fine and had no difficulties. She even thought that her swollen legs were pretty normal. This forced me to refer her to the nearest facility and I even escorted her. Upon reaching the facility, she was welcomed by a nutritionist. She was weighed 82 kgs. Her blood pressure turned out to be very high. At that point, her mother, also realized that there was something wrong with her daughter. After following procedures, the nurse was convinced that the girl needed medical attention. ---</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Cholera During my field work at my community in Nydlenda, I came across a certain family who were very sick with really bad diarrhea and had to be admitted. They said that they had been through a lot, because they did not know the remedy of their sickness. After a few discussions on Cholera and its effect on them, they narrated that they usually buy cooked food alongside the road and sometimes considering hygiene. But they also cooked vegetables without washing and also took fruits, which were not washed or washed in dirty water. So, I educated they that before buying food or fruits you should consider good hygiene by cooking the food well and to wash your hands before and after touching food. ---</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence During the month of April as I was doing my daily health education in my community (Obinga), I came across a woman who had faced mistreatment from her husband many times. When I talked to her, she opened up that the husband had been battering her and even the children to some point. She is always being sent away with the children. I decided to approach the husband, all he said was “don’t meddle in my affairs.” I was touched by the woman’s situation and decided to help her by referring her to the right authorities. I even accompanied her there and helped her explain her situation. I left her with the authorities. ---</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Rape and Pregnancy During my usual work as a community educator at the Nyalenda slums, I came across a certain adolescent girl who was three months pregnant and had not yet started her ANE. While talking to her, in order, to understand the reason as to why she had not started, she confessed it was because she had been raped. She was afraid of the stigma of being raped. She became pregnant, she didn’t want her family and friends to know what she was going through. So, I had to convince her that getting pregnant was not bad, though she was raped and by bad luck she became pregnant. It was a good that she decided to keep the baby and not abort it. So, she needed to start her antenatal appointments for her baby, to make sure the baby was healthy. Also, for her to be tested for other ailments to keep up on her own health status. After two days, I had to do my follow-ups, to see whether the girl went to the hospital or not. I found out the she did go to the hospital and was tested. She was very healthy as was the child. She was very happy that she could have a happy life free from fear. She promised never to miss her ANE clinics. The worst thing is that after being beaten until she couldn’t walk, her phone was seized, so she could not call anyone. The story touched me personally. I reported the man, myself, to a recognized authority, who has been checking on her on a daily basis. This has somehow stopped the assault. ---</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Management (MHM) While conducting my routine dissemination of MHM messages, I met Purity (not her real name), a lady from Salina village whose husband had refused to buy her sanitary pads. Since the lady solely depends on her husband for provisions, she resorted to using old and torn clothes from her closet. This method was neither reliable nor sustainable; therefore, she experienced multiple challenges when her periods were due. Purity was glad to meet me, explained her situation and urged me to meet with her husband. I later met with Purity’s husband and shared MHM messages with him. She explained the importance of men’s participation in MHM and the need for husbands to support their wives when it comes to MHM. The process was painstaking, but later on the husband finally agreed to support his wife. Currently, he’s the one directly buying Purity sanitary pads from me. ---</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Management (MHM) I had been taking a group of young girls from Manyata village between ages 10 and 17 years through the structured six-module Social Behavior Change sessions on MHM. During the discussions, it was noted that the girls used to dispose menstrual waste in pit latrines, which is not a safe disposal method. I articulated proper ways of disposal of menstrual waste, and the girls chose burning as a more user-friendly method. After some time the girls met again for another session. Two girls who had tried burning menstrual waste shared the experience and observed how easy it was. ---</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Management (MHM) I have been conducting MHM awareness in my community when I came across a bodaboda group, which is a predominantly male taxi group who use motorbikes to offer transport services. The 14 members of the group expressed how they don’t participate in MHM at the household level, stating that it was a taboo for men from their community to even talk about menstruation. I took them through an awareness session, focusing on the myths and misconceptions around menstruation and by the time I finished, all 14 members of the group agreed to start supporting their wives and daughters in MHM. Nine of the members bought sanitary pads from me to take to their wives. ---</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Management (MHM) I met a family at Kanyakwar village where Mike (not his real name) never allowed women in his family to work on farms during their menstruation period. He taught them that if one goes against these precautions, crops in the farm would dry up. Mike’s wife loved farming and she’d at times sneak to the farm while on her periods, knowing that her husband was acting out of ignorance. She sought to solve the situation, so, when she met me, she invited me to her home to discuss the issue in the presence of her husband. Mike was receptive, giving me an easy time to take them through the MHM sessions. At the end, Mike was convinced that he had been acting out of wrong conceptions. From then henceforth he allowed women from his household to attend to farm duties during their menstrual periods. ---</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Common Cold During this cold period many people suffer from the common cold, others because of allergies, while others contract colds from other places. Common colds are very common to people who are allergic to cold dust or pollen. One example is that some get colds whenever there is dust. Normally there are remedies such as hot boiled lemon water with ginger. Common colds can be accompanied by a sore throat. When I used this remedy, I became okay. Others confuse the common cold and flu just like they tend to confuse a sore throat with tonsils (tonsillitis). That is why I picked this topic during the cold season to help community members to know the difference. ---</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Fibroids During my usual community work in my area, I came across a woman who has been suffering from fibroids. Unknowingly she opened up to me and told me how it was affecting her life. That each time she has sexual intercourse with her husband, all she feels is pain. I took this personally and took the woman to the hospital. They recommended an ultrasound to find out if it truly was fibroids or any other related disease. The hospital found out that it truly was fibroids and had grown large enough to require surgery. She went through surgery and with God’s grace it turned out to be successful. The lady went home smiling and was relieved of pain. ---</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy As I was conducting my usual field outreach, I met with one young girl, about 13 years old. She had left school as a result of a pregnancy. She was chased away by her mother, since her father died some three years before. She had no information as to the importance of starting her prenatal regimen. I interrogated her about it an she responded that she was shy about it (her pregnancy) due to the stigma. The pregnancy came as a result of being lured with presents from one guy within their residence. Upon realizing her pregnancy, her mother threw her out of their home. I gave her some counselling by which I advised her that getting pregnant was not the end of life or carrier (?) but a new journey in her life development. She accepted this counseling and promised me to visit a health facility for prenatal counseling and medication for future illnesses and to know her health status. I am happy that she is doing what I told her to do. ---</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Diarrhea As I was walking in the community doing health education/sensitization, I came across a certain mother, whose child was experiencing a lot of diarrhea. I had finished giving my health talk and I called her aside. I educated her on the dangers of diarrhea and how best one can control diarrhea. After I counseled her, I referred her to the nearest health facility for further diagnosis for her child. After 2 days when I did follow-ups to check on how the child was faring, I found out that the child was given zinc and (ovs ) for the diarrhea. The mother was so happy on how she was handled at the facility level. She also thanked Wired International for training CHWs so that they can help the community members. ---</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 1, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sexual Health Education Many young people (adolescents) have not better understanding on sexual health issues. I realized this when giving health education on sexual matters. I found out that so many adolescents engaged in sexual activities without knowing or studying their partners well. This has led to unintended pregnancies, abortion, and premature births. Those young adults don’t talk about sexual activities before it occurs which includes limits, contraceptives, condom use, and also the meaning of the relationship. This has led them into wrong marriages with a lot of sexual gender-based violence. They don’t realize that by working through sexual issues, individuals may have psychological and emotional woundings from past experiences and damaging beliefs. This is an area which still needs a lot of efforts by CHWs , in order to prevent more of sexual related issues from affecting the community. ---</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Malaria During my weekly daily outreach in my community, I realized that most of the young kids I my area were mostly sick and were diagnosed with malaria and were on medication. This came to my attention because most of them were younger than 10 years old. Almost all of them had runny noses or the flu. This came to my attention and I had to educate the young women and men about Malaria and its prevention. We discussed the use of mosquito nets which were issued by the government earlier this year. One parent admitted that she had not been layering the net for her kids at night. This contributed to her son getting sick. I also realized that there is so much stagnant water around because we live in a slum where there is little sanitation. I advised them to unclog the stagnant waters or pour paraffin into the stagnant water to avoid the breeding of mosquitos. ---</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Stress Management I wanted to know more about people’s lifestyle in my locality. I decided to walk door to door just to find that many people are struggling with stress and depression. I met a couple who wanted to know more about stress management. I asked them a few questions on what would make them stressful. I taught them about the repercussions of stress and that it can give birth to many chronic diseases. I also taught them how to manage stress and how to adhere to the instructions. They were very happy and very grateful. ---</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Malaria During my sensitization and awareness talks in the community concerning health issues, I came in contact with a lady who complained that she was sick with malaria every now and then. I had a one-on-one with her and she told me that her compound was too bushy and that she was not cutting down the grass in her compound as needed. I also informed her of other preventive measures like the use of ITMN, draining of all stagnant waters, and closing all windows early in the evening. She agreed to practice all the preventive measures. When I did my follow-up, I found out that she practiced all the above and now she is not getting sick with Malaria as she used too. She is happy and thankful for the organization. ---</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Typhoid During my mentorship in the community, I came across a certain household who were complaining of stomach ache, diarrhea, and headache. When I approached them, they said that they drink water from (wigma?), which is untreated. They don’t boil the water, they use it in all domestic ways, but it is making them so sick because the water is used by everyone; even the animals drink there. The animal waste is making it contaminated and hence giving the community typhoid because of contaminated food and water. I sensitized them on the importance of boiling water. People can but water guard, but using local ways help make everyone to be well health-wise. During my follow-ups, I found my people well after they practiced what I told them and they are happy. ---</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>First Aid on Nosebleeds During nosebleeds, blood flows from on/both nostrils. It can be heavy/light and last a few seconds to 15 minutes/longer. In my class, I came across a patient who had nosebleeds and did not know what to do. Therefore, I advised her &amp; gave her some of the solutions like: a) sit down &amp; firmly pinch the soft part of your nose, just above your nostrils for at least 10-15 minutes. b) lean forward and breath through your mouth, this will drain blood into your nose instead of down the back of your throat. c) Place an ice pack on the bridge of your nose. d) Stay upright, rather than lying down as this reduces blood pressure in the blood vessels of your nose &amp; will discourage further bleeding. When I came back for the checkups, my clients were able to put all these into action, hence could help other patients with problems of nosebleeds. ---</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Menstruation Problem When a 15-year school girl saw her first period, she didn’t know what was happening to her. To her, something must have bitten her because the bleeding began during the night hours when she was sleeping. The blood was all over her clothes and she was afraid to wake up and do her daily chores. When her mother came to wake her up, she explained to her what was happening. Her mother could not believe what was happening. Her mother quickly told her to wash, then rushed her to the nearby health centre. The doctor did her diagnosis and found that the child had started her menstrual cycle and advised them on what to do. That is why we as CHWs continue to sensitize the community about menstrual hygiene and what to do. ---</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 1, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Obesity Obesity involves excess body fat that increases health problems. When more calories are taken in and not well synthesized...Most people we meet in the field believe that by having excess body weight, you are healthy. They believe that people with small bodies are not eating well. We advise them to check on their diet and avoid fats. To keep them fit, we advise them to exercise regularly to burn more calories from their bodies. ---</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 1, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Trauma When I had a session about mpox, people had trauma about its mode of transmission. Some said it will not be easy for them to heal fully if in case they acquire it. This is because of the quarantine period when a person has to stay away from others. This might lead to stigmatization. During the healing process, one has to wait until the swollen pimples fall off, leaving much scarring. The caregivers are mostly at risk another parent stated where a family member has it, living in a household containing many family members. The community wishes for a quick solution to reduce the spread of the mpox virus. ---</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Mpox At the end of August, I was educating members of my community about the deadly virus, mpox. It has been confirmed in Kenya with different cases in different towns. I had to explain to them that the virus could be spread from one person to another through close contact by respiratory secretions in the air or on objects and also through skin lesions. This caught them unaware because they thought it was transmitted from monkeys as the name suggested. I had to go ahead and explain to them the mode of transmission from animal to human and human to human. I also educated them on prevention such as washing hands will with soap and water after any contact with an infected person or animal. I also encouraged them to use an alcohol-based hand sanitizer instead of soap and water weren’t available. I advised them to always report to the nearest facility if they had symptoms such as we discussed or skin lesions for easy isolation and treatment. ---</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Malaria As I was doing health education in my area of work which is Bandani, Kombedu, and Kanyamedha, I realized there was a young mother who was really struggling with her baby. She was trying to remove the baby’s clothes because she had a high fever. I called her aside and talked to her about the signs and symptoms of Malaria. After that I referred her to the nearest health facility which was Airport Hospital where the child was tested for malaria. After 2 days I did a follow-up on how the child was doing. The mother was appreciative for the health information we normally pass on to the caregivers in the community. Her daughter was diagnosed with malaria, she was treated and now the child is doing well. ---</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Mental Health As I was sensitizing the community members about health issues at Auji Village, I came across a man who was so withdrawn that he could not help or allow himself to sit in class for the session. He was up and down, walking and talking to himself as the session was going on. I had a one-on-one with the man and he agreed to share with me that his wife had run away with his three children because he had lost his job and could no longer provide for his family. I gave him counseling and later referred him to Airport Hospital for more diagnosis and counseling. He is now doing well. He thanks the organization so much and is very appreciative. ---</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Family Planning Misunderstanding While teaching women about family planning benefits and side effects, I came across a young mother aged 24 years old who was having side effects with family planning methods. The young mother requested a femiplan pill (birth control contraceptives). She was given them at Zaramogi Oginga Odinga Teaching and Referral Hospital when she took her two-month-old kid to the to the clinic. The pill clearly indicated that she was to take 1x1 (one pill a day), but she didn’t understand the precautions about dosages. She ended up taking it 1x3 (3 pills a day) which almost killed her. She became very weak and even began to turn yellow in color. I found her laid out on the floor as if she were dead. I gave her a lot of water and then told her never to take those pills until she had recovered. After two days she was well again but I advised her to go and see a health provider at 300TRH for further observation. ---</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Coaching girls on the importance of menstrual hygiene has brought up a lot of discussion about the physiological changes occurring during the adolescent stages. Menstruation causes the onset of physiological maturity in girls; it became part and parcel of their lives until menopause. Our girls are now in a position to understand that menstrual hygiene is a hygienic practice during menstruation. This practice can prevent girls from infections in their reproductive and urinary tracts. In my community, menstruation is surrounded by myths and misconceptions with a long list of do’s and don’ts for girls. Menstruation and menstrual practices are still clouded by taboos and socio-cultural practices. This results in adolescent girls lacking knowledge and remaining ignorant to the scientific facts and hygienic health practices which could result in adverse health outcomes. ---</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Scabies As I was walking in the field, I met an old woman who was affected with scabies. She said she contracted the is disease while in jail. She was recently released. Because I did not know what it was exactly, I told her to first go to the hospital and get treated. She came and told me what happened when she went to the hospital and was diagnosed with scabies. She was given a full treatment. She was so happy. She is still on medication and her life is improving very well right now. She has thanked me for helping her. She said she did not know what to do to get help. ---</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 1, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 1, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Mpox During this month, I learned that Monkey Pox, which is mpox, is a viral disease caused by the monkey pox virus. In the past I believed that mpox and scabies were one, until later this month when the module was introduced on the Wired website portal on mpox. I came to learn that it’s a zoonic, which means that it can transmitted from animals to humans. Rodents and primates are the primary carriers. This has helped me in my field work because I can respond and teach my participants on the mpox disease including symptoms: such as fever, headaches, muscle aches, and rashes that progress from mucus to pustules which form scabs. ---</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 1, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Urinal Tract Infection As I was doing my daily health talk in my community in the Nyalenda slums, I came across a group of women who were really complaining that their private parts were always itching, even after they were treated with many drugs (Kienyeji) but didn’t have any traits. The session was all about STI and UTI, when their eyes opened and they learned about the types of UTI’s which were caused by sharing toilets with infected people and not practicing hygiene. They learned that sexual transmitted infections were caused by having unprotected sex with infected people. After a long discussion with them, I advised them to seek medication, afterwards practice prevention and good hygiene against these diseases. During my follow-up in this community, I found my client happy and could now tell the difference between UTI and STI. They were so empowered that they became champions to their fellow women in the community. They were really happy to get such important information that transformed their lives. ---</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Adolescents During my health talk in my community, I came across a group of girls who were in their adolescent period. These girls dropped out of school and rented one house which they all stayed together. One of the community members approached me and told me about these girls. The worst part of it was that these girls were not from my area. When I talked to them, I realized they were from the same school. I tried talking to them about the benefits of going to school and that this was just one stage of their lives. I advised them that they might even get pregnant of even (HW)? or STI’s. They took my advice and decided to go back to their parent’s houses and even back to school. When I followed up, I realized that all of them were in school. ---</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Malaria During my activity out in the field, I met a young boy, who was suffering from Malaria. His mother told me that she had been taking him for treatments. I wanted to know more about what kind of treatment she was talking about. I came to understand that she had taking the boy to a quack doctor, who took two hundred shillings for the treatment. The quack doctor had been administering the injections to the boy. She didn’t even take a sample to know what kind of sickness the boy was suffering from. She only looked at the boy and mixed some stuff and injected it into the boy. I advised the mother on how harmful this was to her son’s health. I told her to stop taking the boy to that doctor and to take him to the hospital immediately. She did that and now the boy is on the right medication. She was so happy about the advice and promised not to do that again. ---</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PREP and PEP During this month as I was doing my session around my place of stay in Villah 1,2, &amp; 3 I had a group of young men and women. We talked a bit about HIV/AIDS and this topic led us to issues of PREP and PEP as preventive measures of HIV/AIDS. I discussed the topic as it was the first time getting clarification and differentiation of the two drugs. As I was explaining, the group listened attentively and asked many questions, one after the other. One of the audience, a young man, was interested about PREP, as it was his first time in that session, he asked for help in getting that drug for himself. I did my part and referred him to the KIMRI facility, and he was comfortable with that referral. He is currently on PREP and is even involved in a study about the two drugs. I noticed he could assess his risk of getting HIV/AIDS and now he knows how to prevent it. He came to thank me and the WIRED Organization for the information that he never knew and now he is safe. ---</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Coughing During my day to day in the field I met a young mother who had a cough. She was coughing until blood come out of her mouth mixed with sputum. She had been coughing for about two weeks. She said that she had been buying over the counter drugs with no response. Her health was in bad shape, and she was losing weight. We talked at length about coughing and about Tuberculosis. I advised her to visit the health facility for a check-up. She went to the facility and got help. She is now on drugs and her health has improved. ---</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Malaria It was on Monday night when I heard a neighbour screaming as if someone had died. When I went to her house, I was told that she had a severe case of Malaria and had not visited a hospital, so the malaria was making her scream like a mad woman. I quickly advised the family to take her to the hospital. It was found that she was suffering from cerebral malaria. ---</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Menstruation is something that is experienced by young girls who have attained adolescent stage and women who have not attained menopause stage. In developed countries, the government has put in place good structures that seek to address these challenges which young girls and women go through when they have their monthly periods. School going girls have a hard time finding sanitary pads/towels to use when they are experiencing such incidents. Some use old clothes instead of pads which is demeaning because they have little knowledge of how to dispose of them (soiled clothing) after use. This contributes to poor hygiene within the settlement. This scenario caught my attention as a CHW. I took my time in the field to train both young girls and women, as well as the men, about the importance of proper disposal of sanitary pads after use. I also encouraged the men to make sure that they buy for their daughters and wives sanitary pads/towels, so that they can minimize using old clothes which are unhygienic. From this training, I have seen some of the participants setting up a place for disposal of used sanitary pads/towels. This is a success story for me. ---</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Syphilis It is a sexually transmitted infection that causes infected sores. It is passed through sex without using a condom, sharing needles, or blood transfusions. One of the patients had this disease because she was not using a condom each time she was having sex with multiple partners. I advised her and she promised never to repeat the same mistake again. I also advised pregnant mothers to attend the clinic every time to prevent them from getting syphilis. In case they might have it, without going to the clinic for a checkup, they could pass syphilis on to their unborn child. I assured them that syphilis could be cured, but without treatment it could cause lasting health problems. After all this, they all got the knowledge and promised to put it into action. ---</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Condom Use And Demonstration In the month of October as I was doing my health talk outreach in Manyatta, I came across a group of young men; Boda Boda men. We started talking about HIV/AIDS and eventually reached a point about prevention. We discussed how condoms and PREP usage is a way of prevention HIV/AIDS. We discussed how to use a condom and even got a chance to demonstrate with a penile model. It was at this point that I realized that most of them had been ignoring important information while using a condom. One of them said he had never known about the expiring dates of condoms and how to open a condom package. I eventually explained to them how to correctly and consistently use condoms, and if one cannot use condoms consistently, they should visit the nearest facility for PREP. ---</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>HIV/AIDS As I was doing my weekly sensitization at the community of Kanyamudhu (sp) and Bendini I came across a young man who really wanted to so the HIV testing and counselling. He said that it had been a long time since he was tested. I talked to him, did counselling with him, told him about the benefit of testing, and where best he could get services. After counselling, I referred him to the nearest health facility, where he could get the services. After 3 days of follow-ups, I found out that he was tested and given condoms. He was also initiated in PREP so he could be safer. He was very grateful for the services he got from the facility. ---</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Dental Caries Tooth decay has been a major problem and the community at large wishes for a good solution rather that removal of the teeth. The bacterial process that damages hard tooth structures, causes pain, tooth loss, and infection as stated by an individual who has experienced tooth decay. There is a woman who experienced tooth decay every year, causing her to have teeth removal which led to pain in the process of removal. The woman stated that it would be good if there was another alternative way. The toothpastes used daily which can help, one being Pepsodent, helps as said by another individual during the session. ---</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Nutrition As I was doing my sensitization in the community, I came across a woman who had issues concerning food insecurity. I informed her to prepare a kitchen garden using broken troughs. She had to put soil in the basin, pour water, and then plant the vegetables. She needed to water the plants every day. The other alternative was to rear poultry so that the children could have the food groups needed for their development. I informed her that the children need at least seven food groups out of ten. ---</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Nutrition During this period, I came across a family headed by a child. It was a family of about five children who did not look well. The family lacked enough food which made some of them look malnourished due to poor food. Child-headed households require support in order to ensure their access to basic health and nutrition. There are certain diseases which arise due to inadequate feeding. Proper nutrition is essential in protection from certain diseases. It is important to get access to proper food and nutrition. ---</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Mental Health and Gender-based Violence Sensitization During this month I was working with bodaboda boys and the community. I was granted an opportunity to do GBV sensitization at Migosi hospital and mental health. I was amazed that many people didn’t know when they were being hurt in their marriages, making the situations normal, without knowing that we have referral pathways to reach out to. They should know their rights because some of them, even kids, didn’t know that a boy can be sodomized, not only are girls raped, but boys can also be raped by anyone, be it the parents, uncles, pastors, neighbors, and even friends. They were very happy to learn a lot of things and promised to report in case of any abuse to 1195 which is the number for health care assistance Kenya. ---</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Breast Cancer The month of October being Breast Cancer Awareness month, I decided to teach about breast cancer. Many people did not know about it in the community. I found few women whom I decided to engage in this topic. We were trying to feel the breast for lumps. On specific woman caught my attention. She was complaining that her breasts had been sore for a long time now. She had heavy breasts for over a month. She also stated that within the month her breast grew rapidly. I told her to go for a breast cancer screening, which was free. When we meet again next time, she should give me feedback from the hospital. We also talked about how to prevent women from getting breast cancer. They did not believe that breastfeeding was one of the ways to prevent those cancer cells. They agreed that we would all partake in healthy living to prevent getting any form of cancer. ---</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Malaria As I was going round and sensitizing the community about health issues, I came across a woman who had a child who had been affected by malaria most of the time. When we talked at length, I came to realize that she was not practicing the preventive measures for malaria. I informed her that it was better to prevent the disease than cure it. The preventive measures include draining all the stagnant water, sleeping under treated mosquito nets, slashing the bushy compound, closing the windows and doors earlier in the day before the evening, and not having dirty clothes in the bedroom. The lady has been practicing these preventive measures, and the child is now okay and not getting infected by malaria. ---</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Asthma When I was in the community, I met a mother who had been complaining about her daughter’s poor breathing. I tried to ask her all that she had been experiencing and concluded that she was asthmatic. When I heard her story and with the knowledge I gained from the training, I taught her about asthma. As we all know asthma is a chronic lung condition that is often undiagnosed and under treated. It can cause coughing, wheezing, and difficulty in normal breathing. I told her what could trigger asthma: dust, pollens, fur/feathers, cigarette smoke, and cooking smoke. The girl had a wheezing sound and thus I referred her to the hospital so that she could know more about aid and how to get the drugs or inhaler for the girl. She thanked me as well as the Organization that endorsed us to help the community with all this health knowledge. It is a (bravo?) to Wired Organization. ---</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Sexually Transmitted Infections I was doing health education in Bardani Kumbedu Kanyamedha. She called me and talked to me privately concerning her problem. We talked, I counselled her and educated her on the signs and symptoms of STI’s, modes of transmission, and the preventive measures. After all that health education, I referred her to the nearest health facility where she would get the right services she was hoping to get. After 3 days follow-up, I found out that the girl was now doing fine, she was treated and given medication to help. She really thanked Wired for the good job they have been doing in the community. ---</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Suicidal Thoughts During this holiday when children are at home with their parents, I thought it was important to take them through some mental related issues such as: suicidal thoughts that some of them pass through while at home or in school. In most of informal settlement you find that some parents indulge themselves a lot in taking alcohol, not thinking of how this might affect their children. This has led to some of these children making risky decisions and when harshly corrected, they begin thinking of ways to do away with their lives. As a trained CHW, I teach them possible ways to avoid such thinking in order to reduce cases of suicide among the younger generation. ---</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>HIV Prevention During my mentorship in my community, I came across two couples who were dating and even planning to get married, but the lady was already pregnant. Yet they had never visited a hospital for testing, nor had the lady started her prenatal visits. I had to empower them on the HIV and the importance of testing. We talked about causes of HIV: having unprotected sex, deep kissing when someone has a wound, blood transfusions, and also it found through road accidents when your fluids mix –without forgetting during birth. The conversation went deeper on how or what you can do when you have HIV and your partner doesn’t. ---</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PrEP and PEP Education During my Outreach in Manyadia, I was honoured to teach a group of young men and women. We managed to talk about the benefits of PrEP and PEP. We discussed why it is used i.e. PrEP is used to protect someone from acquiring HIV/AIDS from an unprotected person. This had to push us on “Discordant Couples” who use PrEP and the infected person uses ARVs. This made one of the participants ask to speak to me in private. She opened up and talked about her husband using ARVs while she used PrEP. She had questions about stopping PrEP because her husband had good adherence to ARVs. I advised her to visit the nearest health facility and talk to the right service provider. ---</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 1, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Physical Exercise Physical exercise is very vital, sometimes we tend to ignore it. She could not breath well after walking for a distance of 1 kilometer. I wanted to get into a deep discussion to know where the problem was. In that discussion I realized that most of the time she used a motorbike, even for a short distance. I advised her to start physical training every day for about 15 minutes. She adhered to the rules and now she can walk a distance of 5 kilometers without any problems. She is so grateful for the teachings she received. ---</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 1, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Physical Fitness Physical fitness refers to the ability of the body to perform daily tasks while maintaining optimal health and energy reserves for any unexpected challenges. During my field assignments, I took the young boys through the benefits of physical fitness. For quite of number of days, the boys have been spending their time idling on the estates. Through the support of a ball from Prof. Gary Selnow and Shawn during the recent visit to Kisumu Obunga, the boys have something to keep them together. I got an opportunity to join them in a training where I took them through the benefits of physical fitness. Concerning physical health, the exercises help in reducing the risk of chronic diseases such as diabetes, heart disease, and obesity through strengthening the immune system as well as improving bone density and muscle health. In fact with mental health issues, I shared with the boys that physical fitness eliminated stress and anxiety, leading to improving cognitive function and memory. Being that, I have been struggling with high blood pressure, they are learning from me how I am managing the pressure through physical health. This discussion was very healthy to the young boys. ---</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 1, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Cholera During my field assignment in the small village called Myamrongo in Kibos Community, I came across a small family of a single mother, who has been suffering from Cholera for a period of time. Due to her financial status, she could not afford well cooked food, pure drinking water, and could also not maintain good hygiene. I told her about the shortcomings of drinking unpurified water and eating undercooked foods to her health and that of her children I am glad since my visit to her, she had been maintaining cleanliness and also boiling water before drinking. She has also been making sure that the food she and her family eats is well prepared. ---</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Sports and Health It is very important for any athlete or sports personality to have good health and a basic knowledge on how to take care of themselves in case of an injury during sporting activities. During this reporting period, we met a group of young footballers who have the ambition of becoming great players in the future. To my surprise, the team did not have a physician, or any person trained in First Aid. I was able to take them through the basics of First Aid, in case of an injury during sporting activities. Injuries can cost them their talent if they are not well taken care of. ---</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Malnutrition Most lactating mothers and children under 5 are experiencing undernutrition and overnutrition. This is because of the lifestyle and lack of specific nutrients in the diet. A mother of a one-year old child narrated that when she took her child for a clinic checkup, the results turned out that the child was underweight. She was taken through the proper diet a child needs. The child had fatigue, dizziness, and weak muscles. I managed to further teach other mothers on the importance of nutrition. This enabled the participants to appreciate the programme of sensitization we do in Wired for the community. ---</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Malnutrition It was on Monday when I was doing my field work at Nanga when I came across a mother and her malnourished two-year child. After a long talk with her, she agreed to my referral to Kuap where the child was enrolled in a program where she is under professional health care. I am happy being that the child has now gained an appetite and can now breastfeed and eat without any problems. ---</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>HIV Prevention Individuals can reduce the risk of HIV infections by limiting exposure to risk factors. Here are some of the prevention measures that I give out in the community. Correct penetration can protect against the spread of STI’s and HIV/AIDS. Harm reduction for people who inject drugs can take precautions against becoming infected with HIV by using sterile injecting equipment, e.g. needles, syringes for each injection. Voluntary medical male circumcision which reduces the risk of other sexually transmitted infections. The use of ARVs for preventions. It has been seen that if an HIV positive person is taking ART, they don’t transmit HIV to their uninfected partners. ---</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Flu It has been cold in Kisumu for the past month. Many people have been infected with colds. They tend to mistake this with the flu. Though the symptoms might be the same, the flu and colds are different diseases. Flu can be treated with antibiotics, but it is more deadly than the common cold. Flu affects the lungs, nose, and throat. ---</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene When I was giving out the health information in the community, I had many girls who were experiencing the menstrual cycle. They did not know how to handle themselves. I educated them on how to use the pads and the best way on the proper way to dispose the used pads, to have a good environment. Some of girls were very young and did not even know how to put on the pads or how long they should wear the pads. From Wired Organization, I gave them the very best information on how to handle themselves during this time. I even taught them about the different types of these materials and how to use them. I managed to distribute some to those who were in need. They were very happy. They thanked the Wired Organization for helping the community with the information that the trained community health workers provided. ---</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>GBV In the month of December, I was talking with a group of young girls about GBV (gender-based violence). We ended up discussing the different types of violence. We talked about emotional, physical, and sexual violence. We ended up discussing more about sexual violence. The girls understood that they were susceptible to being defiled by anyone despite the age. We talked about sexual harassment. The girls opened up that most “BodaBoda” men usually harassed them when they passed by. The girls were taught different ways to report violence and where to report violence. ---</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Skin Rashes During the outreach in Obunga, I came across a certain girl who had a child suffering from skin rashes. A condition since birth. She narrated that she had visited different hospitals but there were no changes in her daughter’s condition. She even booked a dermatologist, still no change in the girl’s condition. Yet, when she came to the free medical outreach at Obunga, she has seen changes in her child. Her body is now smooth. She was given a very simple prescription which healed her daughter’s sickness. She is very grateful for Wired International. ---</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Malaria As I was doing my community sensitization and capacity strengthening, I came across a certain teen mother, who was struggling with her baby. She was trying to cool the baby’s temperature with cold water. I called her aside after I had finished giving my health education. I talked to her, counselled her, and educated her about the signs and symptoms of Malaria, the modes of transmission, and ways of treatment. After that, I referred her and her baby to the nearest health facility for further diagnosis. After a follow-up of two days, I found out that the baby had Malaria, she was tested and treated for Malaria. The mother was very grateful for the good we are doing as Wired CHWs. ---</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Malaria As I was going round the community, sensitizing the community members about some health issues, I came across a man who was affected with Malaria most of the time. He said that he was not aware of any preventive measures for Malaria. I informed him it was better to prevent Malaria then to treat it because prevention is so much cheaper than the treatment. The prevention measures included slashing and burning the bushes around the compound, sleeping under nets, draining all the stagnant water, and using mosquito repellants. The man was very happy and is now practicing the Malaria preventive measures. ---</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Sickle Cell Anemia This is a health issue/sickness that is related to the lack of enough blood in the body. During my field work in one of the areas of my community, I came across a young lady with a child who had a sickle cell anemia child. The lady was still young; she never knew her child was anemic. When I looked at the little boy, he did look healthy. Upon asking the mother, she said that she did not know what was happening with her child. Looking at the child, keenly, I concluded that he was anemic. To satisfy m conclusion, I personally took the boy and his mother to the hospital, where he was diagnosed with anemia. Until now, the little boy is still under care of the doctors. ---</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease that if not well taken care of, it can lead to the demise of a human being. The most affected are people from the lake region. It is advisable for us to protect ourselves from malaria. We should always use protective measures such as use of treated mosquito nets and approved insecticides. The most affected are infants, because of parent neglect once they are attacked by the deadly disease. ---</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Measles Measles is a highly contagious viral disease. It affects mostly children, but sometimes it can occur at any age. During my field work, I came across a woman who had a six-year boy. Her boy was showing signs of a high fever, running nose with red watery eyes and he was also coughing. As a CHW having seen these signs before, I suspected that the boy could have been suffering from measles. I told the mother to take him to the nearest health facility for a further checkup. Upon getting into the facility, the boy was found to be suffering from measles. The health officer in charge gave him treatment and after a few days the boy showed healing signs. His mother was very happy and thanked me for the advice I gave her. ---</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Puberty Stages During the December holiday, I took young boys and girls through the puberty stages. Many girls and boys do not know how to take care of themselves during puberty. This is the stage where they experience a lot of changes in their bodies, especially girls. During menstruation, some girls could not master their dates well so they could start their periods during the school days and become ashamed of themselves. When I was handling this topic, I got a lot of questions from my participants on how they could handle the situation, especially mood changes and staying focused in school. I managed to handle all their concerns and answered their questions. Right now, I believe they are going to cope with the changes going forward. ---</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Malaria Malaria had become one of the most dangerous disease in our country/region. I met a client who had been sick for many days. The sickness was on and off again. I wanted to know the reason behind her sickness. She said that she had been buying over the counter drugs whenever she was not in good shape. Be it fever, chills, or headaches, she could not help but buy some painkillers. Little did she know that she had been abusing the drugs by treating the wrong ailment. I advised her to visit the health facility for a proper checkup. She did so, to her surprise she was diagnosed with severe malaria. She was treated well and she is doing fine. She is so grateful to know that malaria can be fatal and promised not to buy over the counter drugs without a doctor’s prescription. ---</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>HIV/AIDS As I was doing health education in different villages, i.e. Bandani, Kombedu, Kanyamedha, Kanyamony and Iwala, I came across a certain lady who have been sickling for about one month and have not gone to the hospital for medical checkup. She waited till I finished giving health education then she came to me and explained that she has been sickling for about one month and she also had several symptoms like loose of appetite, weight loss and she was becoming thin and thin every day. I counseled her and referred her to the nearest health facility where she was counseled again then she was tested of which her test result was +ve. She was counseled again then she was introduced to ART. After a follow up after 2 weeks I found out that she was tested and here result was +ve and she was also given ART. The client was very grateful for the good work CHW’s are doing in the community. ---</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Tuberculosis As a CHW I have done community sensitization for about 3 years with Wired International whereby there was a certain man who was diagnoses with TB on October 2023. The guy was very sick, had no appetite and he was coughing terribly at the community. The guy could not even walk since he was very weak. I referred him to the health care provider where his sputum was taken to laboratory for further diagnosis and when the results came out it was found out that he has TB. He was then introduced to TB drugs by November, 2023 where he could take his drugs as I was doing DOT to him. By DOT to him on a daily basis and checking on him how he was fairing on the guy could not eat and walk and also gained weight within 6 months. By last year November 2024 the guy was now doing well compared to when he had TB. On October, 2023 and all these has been a lesson to other community members that TB has cure and from TB one can still do his normal duties as long as one adhered to drugs without defaulting and from since then the guy is very healthy and living happily without any stress. ---</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Gender-based Violence In the month of January, as I was addressing a group of teenage girls in my community. We managed to talk about gender based violence where we discussed one by one the types of GBV i.e. Emotional, physical and sexual. We majored on the sexual violence because it is affected most of the young girls in my community. The girls managed to open up on different sexual assaults they have experienced but were shying off to report to the authorities. I advised the girls to always report any form of violence to trusted person’s or even a local toll free number that is helping survivors in our local community. The girls understood the importance of report such assaults to avoid occurrence of any sexual violence which may lead to early pregnancy. ---</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Malaria Community health education has brought many impacts in the lives of people in my community. Malaria has been a menace in Manyatta because of poor sanitation and this has led to young children and even infants being infected by malaria. I have managed to do various outreach in relation to malaria management and preventions. One of my neighbors who had a 3 years old kid who had symptoms and signs of malaria. I managed to refer her to the facility but because of the current malaria vaccine given to the kids at the facility the boy was diagnosed with blood infection. He was given medication and the boy is well. The community has also managed to embrace good practices like using mosquito’s nets and slashing and unclogging stagnant water around the homestead. Three households have managed to the same. ---</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Cholera During my sensitization at the community level, I came across a family suffering from cholera due to the environment they lived. The water they drank were never treated and also the food they ate was never cooked well. I taught the family on the benefits and impacts of using untreated water. I am glad they gave me a listening ear and heed to my advice. Until now the family uses clean treated water and also eats well cooked food. Two days ago I visited the family and I was impressed with the outcome. ---</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 1, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>HIV/AIDS In one of the previous months during my fieldwork in my community I came across a HIV/AIDS patient who was on denial stage. I talked to the patient on the benefits of taking ARV drugs but my efforts yielded no seed. I continued talking to her for like three weeks and eventually she gave in but confirmed to me that she could not take the drugs in any of the nearest hospitals; I think it’s because of fear. We talked and agreed that she was to be going to at least a farther hospital away from her area. I personally took the risk of taking her to the hospital of her choice and up to date the lady is taking her drugs in time and perfectly as I also do her follow-ups. ---</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Nosebleed In Africa particularly my Luo tribe associates nosebleed with some cultural perceptions. It’s sometimes very hard to tell those who believe in such myths that nose bleeding (Epistaxis) is connected with medical conditions. Nosebleed can be caused by environmental factors and medical conditions such as dry air, high blood pressure and sinus infections. During my field work engagement sensitizing the members of the community, I was able to perform a first aid for one of the boys who fell down and was nose bleeding at a sporting activity. Having received a basic training in first aid, it was very easy to manage the bleeding thereafter I continued with my session in training them about the management, environmental and medical explanations about nosebleed. After this engagement, the participants understood very well that nosebleed is can be caused by environmental and medical conditions other than cultural perceptions. ---</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Tuberculosis As a CHW I have done community sensitization for over four years with Wired International after I received 15 days Community Health Worker training in the year 2020 February. From the training I received, I have been able to train my community members various health topics which I was taken through and this has enabled me to learn new health modules that are being updated on the wired website. After being assigned to train, I came across a certain man by the name Peter who was diagnosed with TB on March 2021. Mr. Peter was very sick, had no appetite to eat any food and he was coughing terribly and was even afraid to sit in any meetings at the community. Mr. Peter looked very tired and could not even walk well since he was very weak. I asked him if he had been attended to by any doctor or if he had visited any hospital in the previous years which he said yes. I insisted that he get referred again to the health care provider where his sputum was could be taken to laboratory for further diagnosis. I called a doctor at KUAP and shared with him about Peter’s health, the doctor told me to bring him to KUAP so that he could assess him. At KUAP, Peters sputum as taken and when the results came out it was found out that he has TB. He was immediately introduced to TB drugs and advised to come to KUAP for drugs as he continues to monitor him. The doctor asked me to keep on visiting him and help him take his drugs at the right time. By DOT to him on a daily basis and checking on him how he was improving on, Mr. Peter ‘s health started improving as he could now eat well , walk and he gained his weight within 6 months. After taking drugs for six months, Peter’s health improved very well and he could be able to attend and sit at the community meetings and give his contributions. Community members now can learn from Peter community that TB has cure and from TB one can still do his normal duties as long as one adhered to drugs without defaulting and from since then the guy is very healthy and living happily without any stress. ---</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>HIV/AIDS The people in the community more so the ones affected with HIV/AIDS are worried because of the shortage of drugs. Some people have lost hope stating that without the drugs their immunity system will be lowered thus are going to die of AIDS. Women on the other hand are worried about the birth control methods which might not be there and also vaccines of the newborn. They plead with Wired International to continue with outreach to save lives as they also call upon additional services such as family planning methods to be introduced during the outreaches. HIV/AIDS surveillance has helped many people in the community because awareness and measures has helped to reduce case and stigma. Nowadays people can open up about their status without being judged or afraid of what people are going to talk about when it comes to their health. Health facilities have also played a big role by doing follow-up and carrying out reminder activities for the drugs to be taken by the affected individuals. Wired International outreaches being recognized in the community for doing a good job by testing HIV, doing counseling and referrals during the outreaches. ---</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Malaria During my sensitization at the community level. I came across a mother who complained that her child has been having malaria on and off. I educated her on the preventive measures of malaria. The child was to sleep under insecticide treated mosquito net, slush the bushy and burn the compound, draw all the stagnant water around. I told the mother to take the child for more diagnosis and get proper treatment. She has to do good drug adherence, good nutrition and provide treated water for drinking. She then thanks me and the wired organization for good information that saved her baby and thus brings good plans to the organization. ---</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Immunization Status Immunization status has gone up because the community is getting enough information on importance of immunization and its schedule. There are immunizations received at birth, after six weeks, after ten weeks, after fourteen weeks and others. I advised the young parents to take their children to the health centers every month for five years. The information that parents receives from our community health workers makes the numbers of immunizations defaulters to decrease in the community as a whole hence children are growing well. Through wired organization it’s been so grateful for me to work with you thus helping the community get the information that they were not aware of and getting help. ---</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Fungal Infection It is caused by lack of hygiene. For example on the toes of our legs and on the whole body. It is advisable to get a bath earlier before the time that you want to go somewhere to allow your body to get dry well. After bathing thoroughly, dry you with a clean towel, you will be fresh and remain clean often. If you are to war closed shoes, wear cotton socks in dry toes to prevent you from smelling and getting athletes’ foot. If in case you have been affected with athlete’s foot, wash with warm water then apply powder or use histamine medicine. Wash your inner pants each time you bath and hang it on a cloth line on the sun to get rid of germs and to help you to be clean at all times. Hence this prevents you also from itching. Always wear different pants each day after every bath. ---</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Community Health Education The community has been receiving health education and information on different health issues. They have been also gaining skills of life and this has helped them a lot. These education skills have helped the community to have positive changes in some of the areas like; 1. Cholera cases Cholera cases has reduced due to the information and education given to the community members on the importance of water treatment by use of chlorine, by boiling it before drinking and making sure that the vessel that is used to store water is clean. 2. HIV/AIDS The community members have overcome stigmatization because of the information and education that they possess. HIV/AIDS has also decreased because of the use of protective measures e.g. Condoms in male and females, information of guidance and counseling, abstinence. Those who are reactive have to adhere to the drugs. These skills and information as well as education have made the community members to even take good care of themselves. ---</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Gender-based Violence During my daily duty at the field, I met couples were quarreling, insulting each other in front of their children. Neighbors were just staring at them, some were taking videos and photos, and others were laughing as if them watching a free cinema. They were not helping at all. Their kids were crying for help but no one was willing to come to their aid. I went to look for the village elder to help in solving the dispute. We came at the scene and fortunately we were able to calm them down. We wanted to know the essence of their fight, findings were; the husband came home drunk, the kids were hungry, and he uses the whole salary to buy alcohol and stuff to his fellows. We advised them about gender based violence and its repercussions and also alcoholism. The village elder gave them a tough warning and promised to report them to the authorities if they will continue with such. They promised not to do it again and the husband promised to change. ---</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Mental Health Ever since I started teaching and giving people advice about mental health, the suicidal cases have decreased. Men used to keep things by themselves but nowadays they talk and share their views. Women have been empowered to talk and to express themselves whenever they have challenges. I have good reports from three women and two men who were giving up with life, now they have become useful in the society. ---</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Drug Abuse Drug abuse is a common occurrence within our society. Many people engage in drug abuse without knowing the consequences. Most people in our community engage in abuse of drugs that they take to prevent certain diseases. Some of them do so without prescription from the doctor. They only believe that drug abuse entails excessive consumption of alcohol and other substance. We sensitized and informed that taking drugs without doctor’s prescription also drug abuse. Over consumption of over the counter drugs is also dangerous to our health. ---</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>First Aid In November, 2024 in one of my sessions I came across a football team which was carrying out its activities without the services of a team doctor or a physician. Informed them of the need of having someone who will take care of them in case of an injury and they promised to make arrangement of having one. Upon returning to them this month I found out that they secured the services of one of the community members who had a training first aid. The said community member is a volunteer with the team. This has helped them during their training sessions as well as during the games. ---</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Food Insecurity--Nutrition As I was going round in the community sensitizing them on health issues, I came across a household which was having challenges on food insecurity and this resulted when the mother who’s the bread winner lost her work some months back. The woman has a land but she was not willing to plough it and plant some food crops. I sensitized her about the locally available food crops that she can plant like vegetables, fruits, maize crops and others. She agreed to do that and as now the woman has plenty of food in her household and her children are now feeding on the recommended ten food groups. She so appreciative to the organization for educating the community about health issues and life skills. ---</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Community Health Education The community has been receiving health education on different health issues and receiving also life skills. This education has helped the community to have a positive change in the following areas; 1. Malaria Malaria cases has gone down due to the fact that the community is getting information on malaria preventive measures that includes sleeping under treated mosquito nets, slushing and keeping the compound clean, draining all the stagnant waters and children being vaccinated with malaria vaccines. 2. Cholera cases Cholera cases have decreased due to the information and education given to the community members on the importance of water treatment using chlorine or by boiling. 3. HIV/AIDS The community members now does not have stigma about HIV/AID as a result of getting information and education on HIV/AIDS prevention measures, HIV testing and counseling, abstinence and the use of condoms, both male and female. Those who reactive has to have good adherence on drugs. ---</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Scabies As I was in the field I met this child who was infected by scabies. The environment they were living in was not good and they had many lice in their house. We went and did thorough cleaning in their house and even some good people offered her new beddings and the child was taken to a community clinic where she began her medication and as it is right now she is yet to recover from the illness. The woman who was her mother was very happy by whatever we did to her and she promised she will always keep environment clean at all times. ---</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Syphillis In the few years I have worked at wired I have met a few referrals cases but there was one particular one that caught my attention and it was on at topic of syphilis. This case of syphilis involved this beautiful lady who did not know what was happening to her body until we took her to a clinic and she was diagnosed with this disease. She agreed to take on medication and we followed up with the doctor until right now the lady has finished her medication and now she is doing fine and she has agreed to take on preventive measures such as using condom and many others. ---</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene Management During this month, I came across a certain group of school girls who had started their menses and didn’t know how to manage cleanliness and even how to wear it they were doing it the wrong way. I had to empower them on how to wear the sanitary and for how many hours they should wear it which was four hours after there we change and before changing one should wash her hands and after changing also to prevent infections in private parts. They were very happy and said they’ll do everything as told to maintain their hygiene. During this month, I came across 60 girls at Manyatta Arabs who didn’t know how to use sanitary towels and had started their menses. I had to educate them the right way and also it should be changed after four hours and before changing it one should wash her hands and also change and washes her hands so to prevent infection. The students were very happy to be empowered and they said they will empower their fellow students and said thanks to wired international for empowering them and said we should continue helping the community. ---</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Gender-based Violence Young mothers suffer a lot in their marriages. So many are undergoing gender based violence but they are quite about it they fear losing their spouses hence can’t speak out for help. During my field work I have meet so many such cases of which some I referred to the facilities where they can get assisted but still some are in denial state. Some I have managed to gibe counseling and they are now better than before. My findings during this field work is that both men and women still needs empowerment because some men still believe in ruling women as they are used due to the lack of proper marriage counseling so as to get rid of issues of gender based violence. ---</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Family Planning During this month, I self-escorted 13 women to Obunga facility that had given birth and didn’t know the importance of family planning and were interested in it. I sensitized them on different types of family planning like Depo, Pills implant and Coil. Of which they chose different types of each of them and they were initiated on them, most chose implant being for three years and five years was good at spacing. They were very happy that wired international has helped them and they’ll live happily with their families. ---</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Mental Health During this month, I came across a certain family who were traumatized about certain issues that they had three candidates who were sitting for the KCSE. They had high hopes that they would pass their exams but by bas lack all of them failed and got D- both of them which was so hearting to the family and da was scolding them every day which made them to have bad thoughts of even committing suicide. After I visited them and talked to them that failing is not the end of the world, it depends on what are you planning to do with your life and also did referral to the hospital at Migosi so that they are counseled more. After a few days I went back for follow up and found out that they were in good terms with the family and they were really happy. ---</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>HIV/AIDS During this month of January, I came across certain families with different diseases. I came across four family members which I referred for mental health counseling. And also in December I came across certain bodaboda groups 21 of them whom we talked about HIV/AIDS and self-escorted all of them and both were tested at Migosi hospital which made them to be very happy because they had no one to empower them but since wired came in, they are very empowered and can do things the right way. They said that they didn’t know more about HIV/AIDS and after being empowered they can empower their fellows also. ---</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Diarrhea Two patients who were diagnosed with diarrhea were referred for treatment. Follow up was done by the CHW and the patients are now improving and have gone back to their normal duties. They were also advised to complete their treatment and to observe good hygiene. ---</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Family Planning Six women were escorted to Migosi sub-county hospital for family planning initiations, these women had just delivered babies and knew little about family planning. They were empowered by the CHW and accepted to access family planning services. Malaria Another CHW made two (2) referrals to the Obunga Community dispensary. These two men were showing symptoms of malaria and were afraid being that they have not registered with the Social Health Authority (SHA.) They were tested for malaria and given drugs. Followup was made and the CHW found out that they were responding very well and thanked her for assisting them. ---</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Diarrhea There has been an outbreak of diarrhea in children under 5 years in my community. There is a mother of 3 children who asked for my help being that it was on a weekend, I had zinc and oral rehydration salts in my back pack that she could use to control the diarrhea. I the administered zinc and made a solution of ORS as required and showed them how to take it while supervising. After 3 hours the frequency of diarrhea reduced and the children looked more active. As result I managed to control the situation thus they were not taken to the hospital because they recovered well. I also had 6 more cases of diarrhea and vomiting which I referred to the facility in my area and when the result came out the doctor stated that the diarrhea was due to the infection. The doctor gave out zinc and oral rehydration salts which stabilized their condition. ---</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 1, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Poison Another CHW referred one man to Kwoyo health dispensary where the doctor confirmed that he was suffering from poisoning. The man was helped and recovered. ---</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>HIV Testing Ten people were referred for HIV testing where 2 tested HIV positive and were put on drugs. ---</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>STIs During one of the CHW community education sessions on STIs, a young boy who was suffering from STI approached one CHW that he was experiencing the same symptoms that the CHW was teaching. He was escorted by the CHW to Kisumu County Hospital where he was tested and put on Antibiotics. The CHW has been doing frequent follow-ups to find out his progress. He is improving and the parents were also involved to strengthen adherence. ---</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Pregnancy As I was doing my field work in one of the areas in my community during the month of February 2025 there was this girl I came across and she somehow looked different from other girls, simply because she looked absent – minded when I was having my health talk with them. The group consisted of teenage girls and I was teaching about menstrual health. When I finished my lesson with them, I asked to have a private talk with the girl who seemed absent – minded during my lesson. It appears something was wrong with her but did not have the courage to open up to me. That day I did not talk much with her because she seemed emotional but I made sure I knew where she lived. The following day I took my time and looked for the girl. We talked a lot and I later realized that the girl was pregnant and was depressed because if the parents knew about it she would be in hot soup, because she was still a form three student. Since she was also afraid to break the news to her parents, she was planning of abortion. She opened up to me and begged me to help her talk to her parents because she was also afraid of abortion. When I took her to her parents the father sent me way with her daughter blaming me of knowing about the pregnancy. I tried this for like 3 days with the help of some elders and later agreed to listen to me and accepted his daughter with the pregnancy. Because she was still a student I again took her that risk of taking her to her school with the help of the mother and also talked to the teachers who also listened to me as I told them that, that’s not the end of the road for the girl but just a matter of time. Up to date the girl is courageously going to school until the time she’ll put to bed. I am proud of her because the last time I visited her school she was doing better. ---</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Malnutrition As a community health worker I have done a lot and still continue with the health education in the community to make sure that the cases of malnutrition reduces. I have counseled 250 mothers at airport dispensary who have children under the age of 5 years, of the 250 mothers who have under five children, I found 13 children with malnutrition case of which I referred them to the nurse in the same facility for further management as I continued with malnutrition prevention education. Out of 13 children who had malnutrition cases, they were given plumpy nuts and improved flour to increase weight and they were also counseled on the importance of good nutrition. The 13 children are now doing well and am still doing follow – ups to make sure that the mothers with their children maintains good health. ---</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>HIV/AIDS During this month I took my participants through HIV/AIDS session. I was able to sensitize them on the need for proper prevention from the deadly virus. I also informed them on the need for adherence to treatment once you are found to be HIV/AIDS positive. ---</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>HIV/AIDS As a trained CHW and a HIV/AIDS counselor and tester, I was privileged to carry out HIV/AIDS testing services during the community outreaches. In the month of February during the health screening clinics, I managed to test 30 people where 3 people turned HIV positive and were enrolled to care and treatment of HIV at Pandipieri Health clinic. 27 people turned HIV negative and I educated them on HIV prevention. This has given me the opportunity to interact and offer proper guidance and counseling during the community health care service. The Health screening clinics have enabled the community to get medical services closer to them. ---</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Fibroids I encountered two women with fibroid cases. The first woman had severe pain besides her stomach and has been using painkillers. After referral to Russia hospital the gynecologist confirmed that it was fibroids and as taken for surgery. At the moment she is still under medication at bed rest. ---</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Drug Misuse One lady who experienced blood clots during her menses was referred to Russia referral hospital and the doctor found out that she was misusing emergency pills causing hormonal imbalance. She is currently under medication and feeling better. ---</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Subject Unknown I came across three patients who were admitted at Kuoyo health center and got treatment. I have been following their response to the ongoing treatment and found out that they are improving ---</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Self-Referral This month I was the client who was sick. I visited Nyawita medical hospital. I was given medication but did not respond well. When I went back I was admitted and was given IV and after discharge I am recuperating well. ---</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>STIs Three young women with suspected to have an STI were referred to Lumumba health facility where they were treated and they are currently improving. ---</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>STIs After conducting a session on STI’s for 26 participants, four were escorted to the nearest dispensary where the test was conducted through urine sample. Three of them later turned positive and were treated. The other one who turned negative was again referred to sub-county hospital for further management. ---</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Cholera I referred five people out of 46 participants who complained of running stomach to the Kisumu sub-county hospital for cholera diagnosis. They got tested and they turned negative. I continue with cholera prevention and treatment in my subsequent trainings. ---</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 1, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>STIs During this reporting period, I came across two young boys aged 15 and 17 years. They were experiencing some signs of STIs. I referred them to the nearby dispensary for further medical checkup. Upon contacting them, the results turned out to be negative. I advised them on the need for knowing their status and that of their partners. I also told them to use protection all the time. ---</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Child Mistreatment In the month of March, I came across a girl child being mistreated by her step parents. Since they didn’t want her, I took her personally to an orphanage where I do follow ups every day up to date. ---</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>HIV/AIDS In the month of March, I talked to over five hundred people as a CHW concerning HIV/AIDS. Out of five hundred people about 50 people agreed to be referred for HIV testing. Ten people from the 50 people tested HIV positive whereby they agreed to be initiated on ART by the health care provider at Airport health center. When I did follow-up, I found out that the 6 people who were initiated on Art are doing well and they are adhering to antiretroviral therapy. ---</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Child Care Most households had challenges concerning taking care of their children; that is feeding them, educating them and giving them treatment when sick. When sensitization about health issues started, most mothers accepted family planning. Quite a number of them opted for long-term family planning methods and they say this has given them a chance to take care of the existing children. ---</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Family Planning I talked with 11 women on family planning, its benefits and the methods available. Seven agreed and went for the services at the health facility. They are now happy and are willing to sensitize others about family planning. ---</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Diarrhea In the month of March, I referred 2 kids who had diarrheal cases at Kuoyo dispensary. They were treated and luckily no case of cholera was detected. They are currently on medication and practicing proper hand washing together with the mother. ---</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Cholera This month I escorted 6 people who were suffering from cholera at Migosi sub-county hospital upon my follow-ups, they were given medications and were faring well. ---</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 1, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Tuberculosis During month of March, I referred one man from the community to Russia referral hospital for TB diagnosis and he was found to have the disease. He was given medicine and I am doing follow ups every week to confirm his status and how he is coping with the drugs. From what he shared with me after going to hospital, he is seeing changes and promised to take the drugs as he was advised. ---</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Pneumonia There is a woman who has been having body aches and back pains so I referred her to Kuoyo dispensary where the doctor monitored her and found out she was developing pneumonia. She was given medication and she is doing well. Another adolescent also opened up on having leg cramps starting from the upper thighs so when I referred her to Kuoyo dispensary, the doctor found out that she has been diagnosed with pneumonia and she is still under medication. There is a business woman who is elderly, who normally wake up very early in the morning to go to the market who also had chest pains and body aches so when I referred her to Kuoyo dispensary the doctors found out she was developing pneumonia and was put under medication. At the moment her health is improving. She was also advised to put on heavy clothes and socks to avoid such cases. Having come across three cases of pneumonia from an elderly, adolescent and middle aged woman, I referred them to Kuoyo dispensary and was given medication currently they are doing well. ---</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 1, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>HIV/AIDS As I was teaching about HIV/AIDS, I had a client who had decided not to continue taking his ARV’s because of the side effects he was experiencing. I took him through counselling not only on HIV/AIDS but also nutrition. After that, I took him to where he was taking his medication, which is Lumumba health center and helped him discuss the side effects with the health provider. He was assisted and we therefore talked about adherence to medication. Right now, he is responding well with the medication though the side effects are still there hence minimal. In addition, the patient used to abuse drugs like miraa and alcohol but nowadays the patient is not abusing any drug. In the community at field work, I had a client who was a defaulter. I took him to Lumumba health center where he was taking his medication for further treatment. I have been doing follow up and the patient is responding positively in spite of the side effects. ---</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Cholera Many people still do not know the difference between cholera and typhoid symptoms. The headaches and the running stomach together with fever most people when they experience this they say they have typhoid and in real sense it is cholera. I talked to a few women in the community and when we talked deeply about cholera they understood the difference and most importantly they understood why it is more important to visit the hospital and not diagnose any disease by yourself. We all agreed that we will always frequent the hospital in case of an illness that cannot be treated through first AID. ---</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Common Cold I referred one person to Nyawita medical she had common cold. She was treated and given medicine. She went home feeling a bit relieved but still continuing with medications. ---</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Mental Health May is the mental health awareness month so as a community health worker our work is to sensitize the society on the same. I have come to a realization that mental disorder is not only affecting adults but also young people. I was doing my research to understand why depression is rampant nowadays. I made a session with both the youth and adult separately and they were both speaking one language. I asked them the courses of depression. The response was as follows: unemployment, family matters, and broken relationships. We discussed at length and we came to a conclusion that everyone needs help. I shared with them on how to manage stress and they were happy. Two young men who came to this session so frustrated and depressed with suicidal thoughts. They got help and they are doing well now. ---</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Malaria In the month of May, I held a malaria sensitization session in Obunga informal settlement, the activity was part of wired broader efforts to improve public health outcomes. In the informal settlement with that aim to share knowledge of malaria prevention, promote tiredly reduce of case of malaria. I engaged the community in identifying and eliminating mosquito breeding grounds. Through training (practical’s) through the dialogue health talk participants shared their experience with malaria and other breeding sites. The community faces challenges such as limited resources for prevention and mosquito net distribution. Financial constraints also make it difficult to access health facilities. It is recommended to increase the number of sensitization sessions to reach more residents of Obunga. Additionally, strengthening the engagement of community health volunteers is essential to support follow-up activities and community outreach. ---</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 1, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Malaria Malaria Sensitization in Obunga was a successful and impactful events that saw 40 residents of Obunga facilitated with knowledge and referred to health facilities to be helped with malaria preventive tools, which will be key to reducing malaria incidence in Obunga. Three community members were also referred to seek wired international outreach. ---</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>HPV Vaccine During one of my sessions, I found out that some parents /caregivers are still having doubts on Human Papilloma Virus vaccine being given to young girls. I was taking my audience through signs/symptoms of cervical cancer and also the importance of having screened early to detect any sign of cervical cancer. I got so many questions as to why children are being given HPV vaccine instead of adults. These questions came about because parents have a lot of doubts. Many parents express concerns about the potential side effects of HPV vaccines including reactions like pain, swelling or fever. Some parents were also unsure about the likelihood of these side effects occurring. I managed to answer all the questions and encouraged those who refused to allow the children get vaccinated. After the class ended I received a phone call later in the evening from the caregiver seeking to know a place where their girls can be vaccinated. I referred them to District Hospital where they got services free of charge. The two caregivers went back home very satisfied with what the nurses and I at the hospital told them. ---</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Drug and Alcohol Abuse In one of my sessions within the month of May, I was teaching my participants about drugs and substance abuse and as I was taking them through the module, I shared with them my personal experience about the effects of drugs and substance abuse which I went through during the time I was drinking heavily, and how I got myself into diagnosed with high blood pressure as a result of drinking alcohol. Some of the participants were aware that I used to drink locally brewed alcohol in the past with them but were so much concerned to know how I got rid of alcohol. Despite a lot of government intervention to eradicate alcohol in the informal settlement of Obunga, we still see a big number of our youths misusing these drugs due to the fact that they are brewed and sold locally within the settlement. I shared with them about the CHW training I underwent which was organized by wired international, the training that was an eye opener towards changing my habit of drinking. Through the training, I learnt about the effects of drinking too much alcohol and the benefits of quitting alcohol. They were so much happy from my sharing and some of them approached me after the training to seek my help on how they can quit drinking. ---</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 1, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Mental Health Within the month of May 2025, I reached out to 416 people among the participants were 127 males while 289 were female of different age groups. I made 3 referrals to Amani Counselling Center for psychological support. The 3 were male young youths of ages 18 – 23 years old. I am continuing following up on how they are coping up with the counselling. ---</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Water Treatment Water is an essential need in our daily life. It helps to keep our body healthy and fit. It contributes large portions in the formation of blood, without water our body system cannot function properly. It is also important to note that we should not consume any other water but consume water which is clean and safe. Dirty water contains a lot of germs and bacteria that causes diseases such as cholera, bilharzia and amoeba. That’s why it is important to consume safe water which is treated. Treatment of water is important because it kills germs and other forms of diseases found in water. We informed our participants to ensure that they consume clean and safe water on daily basis. Most people in our community consume unclean and safe water for cleaning and drinking. We urged them to begin the practice of using and consuming safe water to avoid diseases arising from dirty water. ---</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene During my field work in one of the sessions where I was teaching about menstrual hygiene I talked about hygiene during menstruations. Since my class also contained men, they were really happy about the topic I was teaching. Some men complained about their wives producing bad odor during their menstrual period. I clarified on the importance of observing hygiene during that period. A menstruating woman should wash her vagina very well when changing her pads to prevent some infections and also when changing her pads should make sure her hands are very clean or well washed. After the end of my session, I also engaged a one-on-one talk with men in my class. They realized that they are also indirect menstruators and promised to help their wives emotionally or physically during their periods. They also came to know that menstruation is not a woman’s thing rather it’s natural. They also promised to buy their wives or girlfriend pads. ---</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 1, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 0, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Nutrition As a community health worker, I have been walking in different villages giving health education. As I was giving health education on nutrition I came across three women with their kids who were malnourished. After the health education I called them aside talked to them and counselled them on the importance of nutrition whereby I took their children’s MUAC and found out the children were having severe malnutrition, I referred them to the nearest health facility that is Airport health center for further check –up. After three days when I was doing follow-ups, I found out that the children were given plumpy nuts and improved flour so that their mothers can make for the children the nutritious porridge and maintain giving them plumpy nuts to boost their immunity. In this month of May I gave health education to about 250 community members where as I found out that there were cases of malnutrition and out of the 250 community members there were 10 children whom I referred for nutrition support since they were severely malnourished. The 10 children were given flour and plumpy nuts with the service provider at Airport health Center and they are now doing well. ---</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 1, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Importance of Immunization When I was going round in the community sensitizing community members on health issues, I came across a mother who has not been taking her child for immunizations. She opened up and shared with me that their church does not allow them to go to health centers or hospitals for treatments and immunizations. After receiving the message on the importance of immunizations she agreed to take her child to the health center then gave her the referral letter. She took the child for immunization and now feels happy and thanks the organization for the good work being done by CHWs. ---</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 1, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Water Treatment Most households were not treating water as they were saying that tapped water has already been treated. I shared with them the importance of water treatment and gave out the tablets for treating water and they agreed to treat water now. There could be breakages of pipes and the clean water gets contaminated and this can result into disease outbreaks like cholera, diarrhea, typhoid and others. Now almost 80% of the households are now treating water and the rate of diarrheal cases has gone down. Most households are linked to a Health Center in case they lack water treatment tablets and in case of any diarrhea outbreak. ---</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 1, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 0, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 1, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 1, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 0, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 0, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 1, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Health Education During this month of May, I reached out 584 people with health education from Migosi and out of that number, 180 were males and 404 were females. We talked about different types of sicknesses and different situations that happens in our livelihoods and in our communities and what rarely and mostly affect us. Mostly we talked about gender-based violence that most of us go through it and they don’t have knowledge of what they’re going through. We also talked about HIV prevention and stigma in our communities that is making our people to die because they fear taking the ant- retro viral that can help suppress the viral load and also making the person to live longer but due to lack of knowledge our people are defaulting the medication making the viral load to multiply and hence causing health living our children orphans. And after our children have remained orphans, they go through a lot affecting their mental wellness leading them to gender based violence while some of them doesn’t understand the meaning of being molested hence leaving with the scars in their hearts. Managed to refer six girls at Migosi hospital for counselling at gender-based office which after some period I went for follow – ups and found them very healthy and sound were very happy and thanked wired international for education CHW to help the community. ---</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 1, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 1, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 1, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 1, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 1, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 1, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 1, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 1, 'Infectious Disease Prevention': 1, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Outreach This month of May, I managed to reach out to 584 people in my community of which 180 were male and 404 were females and referred 6 people to Migosi hospital for counselling at Gender Based Office. ---</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 0, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 1, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 0, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 0, 'Children Served': 0, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 1, 'Families Served': 0, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 0, 'Social Isolation or Emotional Distress': 0, 'Disease Burden': 0, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 0, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 0, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Mental Health During my sensitization this month in the community I found a single mother who was really stressed up and could not carry out her duties as usual. This woman had three children who are still young and are going to school. Being that she doesn’t have a good job and economy is too high she develops a lot of stress in her life and she is very weak. I cancelled her and teach her on how she can manage herself with the children because the more she thanks she will be depressed. I talked to one of the counsellors from the facility and she went to talk to her move about life. After two weeks when I visited her, I found that she started business of charcoal and at least she can get how to manage some of her bills. This was a god move thus she was happy to see her kids go to school however much they are struggling. In our community people are going through a lot and the struggles might lead to mental health if not managed. Through Wired training, I referred a woman for counselling at Airport facility, and she was helped before she got depressed. A big applause to our organization and their CHW for the information they are giving out in the community to help our people. ---</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>{'CHW Empowered Through Training': 1, 'Menstrual Hygiene Education and Challenges': 0, 'Drug Abuse: Environment and Awareness': 0, 'CHW-Led Infectious Disease Management': 0, 'Water Quality, Sanitation, and Hygiene': 0, 'Personal Disease Management and Adherence': 0, 'Nutrition Education and Food Access': 0, 'Sexual and Reproductive Health Education': 0, 'Gender-Based Violence (GBV) and Child Protection': 0, 'Health Literacy and Misconceptions': 0, 'Mental Health Awareness and Support': 1, 'Referrals and Advocacy': 1, 'Handing out Medical Supplies ': 0, 'Monitoring and Follow-Up': 1, 'Bridge Between Community and Health System': 0, 'Clinical Interventions by CHWs': 0, 'Mother and Infant Care': 0, 'Direct Clinical Outcomes': 1, 'Children Served': 1, 'Elderly Served': 0, 'Women Served': 1, 'Men Served': 0, 'Families Served': 1, 'Marginalized Groups Served': 1, 'Lack of Financial Resources for Healthcare': 1, 'Social Isolation or Emotional Distress': 1, 'Disease Burden': 1, 'Stigma or Discrimination': 0, 'Lack of Resources': 0, 'Systemic Barriers': 1, 'Overburdened CHWs': 0, 'Lack of Knowledge': 0, 'Group Based Health Education': 0, 'Individualized Support and Health Education': 1, 'Cholera Education and Prevention': 0, 'Direct Intervention for Cholera Cases': 0, 'Diabetes Education and Prevention': 0, 'HIV/AIDS Education and Prevention': 0, 'Infectious Disease Prevention': 0, 'Tuberculosis Education and Prevention': 0}</t>
         </is>
       </c>
     </row>
